--- a/research/traditional_assets/database/data/bermuda/bermuda_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_business_consumer_services.xlsx
@@ -1133,43 +1133,43 @@
         <v>104</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>168.097108406472</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.07235294117647061</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>8.609999999999999</v>
       </c>
       <c r="L2">
-        <v>8.609999999999999</v>
+        <v>8.523182059894779</v>
       </c>
       <c r="M2">
         <v>3.78</v>
       </c>
       <c r="N2">
-        <v>3.78</v>
+        <v>3.77928205989478</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.0861</v>
       </c>
       <c r="Q2">
         <v>0.0978608650872024</v>
       </c>
       <c r="R2">
-        <v>0.0978608650872024</v>
+        <v>0.09790586508720241</v>
       </c>
       <c r="S2">
         <v>0.06368110587651871</v>
@@ -1191,13 +1191,13 @@
         <v>0.0978608650872024</v>
       </c>
       <c r="X2">
-        <v>0.0978608650872024</v>
+        <v>0.0983867324113156</v>
       </c>
       <c r="Y2">
         <v>0.953513027092749</v>
       </c>
       <c r="Z2">
-        <v>0.953513027092749</v>
+        <v>0.963144471810858</v>
       </c>
       <c r="AA2">
         <v>0</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0978608650872024</v>
+        <v>0.09790586508720242</v>
       </c>
       <c r="C2">
-        <v>8.609999999999999</v>
+        <v>8.523182059894785</v>
       </c>
       <c r="D2">
-        <v>3.779999999999999</v>
+        <v>3.779282059894784</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.0861</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.0861</v>
       </c>
       <c r="G2">
         <v>4.83</v>
@@ -1451,28 +1451,28 @@
         <v>0.728</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.00433083</v>
       </c>
       <c r="N2">
-        <v>0.728</v>
+        <v>0.72366917</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.728</v>
+        <v>0.72366917</v>
       </c>
       <c r="Q2">
-        <v>1.19</v>
+        <v>1.18566917</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0978608650872024</v>
+        <v>0.09838673241131557</v>
       </c>
       <c r="T2">
-        <v>0.9535130270927493</v>
+        <v>0.9631444718108579</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>168.0971084064717</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09790586508720242</v>
+        <v>0.09795086508720241</v>
       </c>
       <c r="C3">
-        <v>8.523182059894785</v>
+        <v>8.436364392456298</v>
       </c>
       <c r="D3">
-        <v>3.779282059894784</v>
+        <v>3.778564392456298</v>
       </c>
       <c r="E3">
-        <v>0.0861</v>
+        <v>0.1722</v>
       </c>
       <c r="F3">
-        <v>0.0861</v>
+        <v>0.1722</v>
       </c>
       <c r="G3">
         <v>4.83</v>
@@ -1533,28 +1533,28 @@
         <v>0.728</v>
       </c>
       <c r="M3">
-        <v>0.00433083</v>
+        <v>0.00866166</v>
       </c>
       <c r="N3">
-        <v>0.72366917</v>
+        <v>0.71933834</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.72366917</v>
+        <v>0.71933834</v>
       </c>
       <c r="Q3">
-        <v>1.18566917</v>
+        <v>1.18133834</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09838673241131557</v>
+        <v>0.09892333172163512</v>
       </c>
       <c r="T3">
-        <v>0.9631444718108579</v>
+        <v>0.9729724766252544</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>168.0971084064717</v>
+        <v>84.04855420323587</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09795086508720241</v>
+        <v>0.0979958650872024</v>
       </c>
       <c r="C4">
-        <v>8.436364392456298</v>
+        <v>8.349546997529234</v>
       </c>
       <c r="D4">
-        <v>3.778564392456298</v>
+        <v>3.777846997529235</v>
       </c>
       <c r="E4">
-        <v>0.1722</v>
+        <v>0.2583</v>
       </c>
       <c r="F4">
-        <v>0.1722</v>
+        <v>0.2583</v>
       </c>
       <c r="G4">
         <v>4.83</v>
@@ -1615,28 +1615,28 @@
         <v>0.728</v>
       </c>
       <c r="M4">
-        <v>0.00866166</v>
+        <v>0.01299249</v>
       </c>
       <c r="N4">
-        <v>0.71933834</v>
+        <v>0.71500751</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.71933834</v>
+        <v>0.71500751</v>
       </c>
       <c r="Q4">
-        <v>1.18133834</v>
+        <v>1.17700751</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09892333172163512</v>
+        <v>0.09947099493526021</v>
       </c>
       <c r="T4">
-        <v>0.9729724766252544</v>
+        <v>0.9830031207141745</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>84.04855420323587</v>
+        <v>56.03236946882392</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0979958650872024</v>
+        <v>0.0980408650872024</v>
       </c>
       <c r="C5">
-        <v>8.349546997529234</v>
+        <v>8.262729874958406</v>
       </c>
       <c r="D5">
-        <v>3.777846997529235</v>
+        <v>3.777129874958407</v>
       </c>
       <c r="E5">
-        <v>0.2583</v>
+        <v>0.3444</v>
       </c>
       <c r="F5">
-        <v>0.2583</v>
+        <v>0.3444</v>
       </c>
       <c r="G5">
         <v>4.83</v>
@@ -1697,28 +1697,28 @@
         <v>0.728</v>
       </c>
       <c r="M5">
-        <v>0.01299249</v>
+        <v>0.01732332</v>
       </c>
       <c r="N5">
-        <v>0.71500751</v>
+        <v>0.7106766799999999</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.71500751</v>
+        <v>0.7106766799999999</v>
       </c>
       <c r="Q5">
-        <v>1.17700751</v>
+        <v>1.17267668</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09947099493526021</v>
+        <v>0.1000300677991692</v>
       </c>
       <c r="T5">
-        <v>0.9830031207141745</v>
+        <v>0.9932427365549473</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>56.03236946882392</v>
+        <v>42.02427710161793</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0980408650872024</v>
+        <v>0.09808586508720241</v>
       </c>
       <c r="C6">
-        <v>8.262729874958406</v>
+        <v>8.175913024588747</v>
       </c>
       <c r="D6">
-        <v>3.777129874958407</v>
+        <v>3.776413024588746</v>
       </c>
       <c r="E6">
-        <v>0.3444</v>
+        <v>0.4305</v>
       </c>
       <c r="F6">
-        <v>0.3444</v>
+        <v>0.4305</v>
       </c>
       <c r="G6">
         <v>4.83</v>
@@ -1779,28 +1779,28 @@
         <v>0.728</v>
       </c>
       <c r="M6">
-        <v>0.01732332</v>
+        <v>0.02165415</v>
       </c>
       <c r="N6">
-        <v>0.7106766799999999</v>
+        <v>0.7063458499999999</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.7106766799999999</v>
+        <v>0.7063458499999999</v>
       </c>
       <c r="Q6">
-        <v>1.17267668</v>
+        <v>1.16834585</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1000300677991692</v>
+        <v>0.1006009106181078</v>
       </c>
       <c r="T6">
-        <v>0.9932427365549473</v>
+        <v>1.003697923255526</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>42.02427710161793</v>
+        <v>33.61942168129435</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09808586508720241</v>
+        <v>0.09813086508720241</v>
       </c>
       <c r="C7">
-        <v>8.175913024588747</v>
+        <v>8.089096446265302</v>
       </c>
       <c r="D7">
-        <v>3.776413024588746</v>
+        <v>3.775696446265301</v>
       </c>
       <c r="E7">
-        <v>0.4305</v>
+        <v>0.5166000000000001</v>
       </c>
       <c r="F7">
-        <v>0.4305</v>
+        <v>0.5166000000000001</v>
       </c>
       <c r="G7">
         <v>4.83</v>
@@ -1861,28 +1861,28 @@
         <v>0.728</v>
       </c>
       <c r="M7">
-        <v>0.02165415</v>
+        <v>0.02598498</v>
       </c>
       <c r="N7">
-        <v>0.7063458499999999</v>
+        <v>0.7020150199999999</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0.7063458499999999</v>
+        <v>0.7020150199999999</v>
       </c>
       <c r="Q7">
-        <v>1.16834585</v>
+        <v>1.16401502</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1006009106181078</v>
+        <v>0.1011838990289387</v>
       </c>
       <c r="T7">
-        <v>1.003697923255526</v>
+        <v>1.014375560736967</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>33.61942168129435</v>
+        <v>28.01618473441195</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0981308650872024</v>
+        <v>0.0981758650872024</v>
       </c>
       <c r="C8">
-        <v>8.089096446265302</v>
+        <v>8.002280139833237</v>
       </c>
       <c r="D8">
-        <v>3.775696446265302</v>
+        <v>3.774980139833239</v>
       </c>
       <c r="E8">
-        <v>0.5165999999999999</v>
+        <v>0.6026999999999999</v>
       </c>
       <c r="F8">
-        <v>0.5165999999999999</v>
+        <v>0.6026999999999999</v>
       </c>
       <c r="G8">
         <v>4.83</v>
@@ -1943,28 +1943,28 @@
         <v>0.728</v>
       </c>
       <c r="M8">
-        <v>0.02598498</v>
+        <v>0.03031581</v>
       </c>
       <c r="N8">
-        <v>0.7020150199999999</v>
+        <v>0.69768419</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0.7020150199999999</v>
+        <v>0.69768419</v>
       </c>
       <c r="Q8">
-        <v>1.16401502</v>
+        <v>1.15968419</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1011838990289387</v>
+        <v>0.1017794248249488</v>
       </c>
       <c r="T8">
-        <v>1.014375560736967</v>
+        <v>1.025282824830913</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.01618473441196</v>
+        <v>24.01387262949597</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09817586508720239</v>
+        <v>0.0982208650872024</v>
       </c>
       <c r="C9">
-        <v>8.002280139833237</v>
+        <v>7.915464105137841</v>
       </c>
       <c r="D9">
-        <v>3.774980139833239</v>
+        <v>3.774264105137841</v>
       </c>
       <c r="E9">
-        <v>0.6027</v>
+        <v>0.6888</v>
       </c>
       <c r="F9">
-        <v>0.6027</v>
+        <v>0.6888</v>
       </c>
       <c r="G9">
         <v>4.83</v>
@@ -2025,28 +2025,28 @@
         <v>0.728</v>
       </c>
       <c r="M9">
-        <v>0.03031581</v>
+        <v>0.03464664</v>
       </c>
       <c r="N9">
-        <v>0.6976841899999999</v>
+        <v>0.69335336</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0.6976841899999999</v>
+        <v>0.69335336</v>
       </c>
       <c r="Q9">
-        <v>1.15968419</v>
+        <v>1.15535336</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1017794248249488</v>
+        <v>0.1023878968339157</v>
       </c>
       <c r="T9">
-        <v>1.025282824830913</v>
+        <v>1.036427203361684</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.01387262949596</v>
+        <v>21.01213855080897</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0982208650872024</v>
+        <v>0.09826586508720242</v>
       </c>
       <c r="C10">
-        <v>7.915464105137841</v>
+        <v>7.82864834202451</v>
       </c>
       <c r="D10">
-        <v>3.774264105137841</v>
+        <v>3.77354834202451</v>
       </c>
       <c r="E10">
-        <v>0.6888</v>
+        <v>0.7748999999999999</v>
       </c>
       <c r="F10">
-        <v>0.6888</v>
+        <v>0.7748999999999999</v>
       </c>
       <c r="G10">
         <v>4.83</v>
@@ -2107,28 +2107,28 @@
         <v>0.728</v>
       </c>
       <c r="M10">
-        <v>0.03464664</v>
+        <v>0.03897746999999999</v>
       </c>
       <c r="N10">
-        <v>0.69335336</v>
+        <v>0.68902253</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>0.69335336</v>
+        <v>0.68902253</v>
       </c>
       <c r="Q10">
-        <v>1.15535336</v>
+        <v>1.15102253</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1023878968339157</v>
+        <v>0.1030097418540686</v>
       </c>
       <c r="T10">
-        <v>1.036427203361684</v>
+        <v>1.047816513288736</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.01213855080897</v>
+        <v>18.67745648960797</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09826586508720242</v>
+        <v>0.09831086508720241</v>
       </c>
       <c r="C11">
-        <v>7.82864834202451</v>
+        <v>7.741832850338764</v>
       </c>
       <c r="D11">
-        <v>3.77354834202451</v>
+        <v>3.772832850338764</v>
       </c>
       <c r="E11">
-        <v>0.7748999999999999</v>
+        <v>0.8609999999999999</v>
       </c>
       <c r="F11">
-        <v>0.7748999999999999</v>
+        <v>0.8609999999999999</v>
       </c>
       <c r="G11">
         <v>4.83</v>
@@ -2189,28 +2189,28 @@
         <v>0.728</v>
       </c>
       <c r="M11">
-        <v>0.03897746999999999</v>
+        <v>0.04330829999999999</v>
       </c>
       <c r="N11">
-        <v>0.68902253</v>
+        <v>0.6846917</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>0.68902253</v>
+        <v>0.6846917</v>
       </c>
       <c r="Q11">
-        <v>1.15102253</v>
+        <v>1.1466917</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1030097418540686</v>
+        <v>0.1036454056524471</v>
       </c>
       <c r="T11">
-        <v>1.047816513288736</v>
+        <v>1.059458918991944</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.67745648960797</v>
+        <v>16.80971084064718</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09831086508720241</v>
+        <v>0.0983558650872024</v>
       </c>
       <c r="C12">
-        <v>7.741832850338764</v>
+        <v>7.655017629926239</v>
       </c>
       <c r="D12">
-        <v>3.772832850338764</v>
+        <v>3.772117629926239</v>
       </c>
       <c r="E12">
-        <v>0.861</v>
+        <v>0.9470999999999999</v>
       </c>
       <c r="F12">
-        <v>0.861</v>
+        <v>0.9470999999999999</v>
       </c>
       <c r="G12">
         <v>4.83</v>
@@ -2271,28 +2271,28 @@
         <v>0.728</v>
       </c>
       <c r="M12">
-        <v>0.04330829999999999</v>
+        <v>0.04763912999999999</v>
       </c>
       <c r="N12">
-        <v>0.6846917</v>
+        <v>0.68036087</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>0.6846917</v>
+        <v>0.68036087</v>
       </c>
       <c r="Q12">
-        <v>1.1466917</v>
+        <v>1.14236087</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1036454056524471</v>
+        <v>0.1042953540305645</v>
       </c>
       <c r="T12">
-        <v>1.059458918991944</v>
+        <v>1.071362951789606</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.80971084064718</v>
+        <v>15.28155530967925</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0983558650872024</v>
+        <v>0.09840086508720239</v>
       </c>
       <c r="C13">
-        <v>7.655017629926239</v>
+        <v>7.568202680632687</v>
       </c>
       <c r="D13">
-        <v>3.772117629926239</v>
+        <v>3.771402680632686</v>
       </c>
       <c r="E13">
-        <v>0.9470999999999999</v>
+        <v>1.0332</v>
       </c>
       <c r="F13">
-        <v>0.9470999999999999</v>
+        <v>1.0332</v>
       </c>
       <c r="G13">
         <v>4.83</v>
@@ -2353,28 +2353,28 @@
         <v>0.728</v>
       </c>
       <c r="M13">
-        <v>0.04763912999999999</v>
+        <v>0.05196996</v>
       </c>
       <c r="N13">
-        <v>0.68036087</v>
+        <v>0.67603004</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>0.68036087</v>
+        <v>0.67603004</v>
       </c>
       <c r="Q13">
-        <v>1.14236087</v>
+        <v>1.13803004</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1042953540305645</v>
+        <v>0.10496007396273</v>
       </c>
       <c r="T13">
-        <v>1.071362951789606</v>
+        <v>1.083537530787215</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.28155530967925</v>
+        <v>14.00809236720598</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09840086508720239</v>
+        <v>0.09844586508720241</v>
       </c>
       <c r="C14">
-        <v>7.568202680632687</v>
+        <v>7.481388002303976</v>
       </c>
       <c r="D14">
-        <v>3.771402680632686</v>
+        <v>3.770688002303976</v>
       </c>
       <c r="E14">
-        <v>1.0332</v>
+        <v>1.1193</v>
       </c>
       <c r="F14">
-        <v>1.0332</v>
+        <v>1.1193</v>
       </c>
       <c r="G14">
         <v>4.83</v>
@@ -2435,28 +2435,28 @@
         <v>0.728</v>
       </c>
       <c r="M14">
-        <v>0.05196996</v>
+        <v>0.05630079</v>
       </c>
       <c r="N14">
-        <v>0.67603004</v>
+        <v>0.67169921</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>0.67603004</v>
+        <v>0.67169921</v>
       </c>
       <c r="Q14">
-        <v>1.13803004</v>
+        <v>1.13369921</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.10496007396273</v>
+        <v>0.1056400748128763</v>
       </c>
       <c r="T14">
-        <v>1.083537530787215</v>
+        <v>1.09599198516408</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.00809236720598</v>
+        <v>12.93054680049783</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09844586508720241</v>
+        <v>0.0987008650872024</v>
       </c>
       <c r="C15">
-        <v>7.481388002303976</v>
+        <v>7.391243269238157</v>
       </c>
       <c r="D15">
-        <v>3.770688002303976</v>
+        <v>3.766643269238156</v>
       </c>
       <c r="E15">
-        <v>1.1193</v>
+        <v>1.2054</v>
       </c>
       <c r="F15">
-        <v>1.1193</v>
+        <v>1.2054</v>
       </c>
       <c r="G15">
         <v>4.83</v>
@@ -2517,45 +2517,45 @@
         <v>0.728</v>
       </c>
       <c r="M15">
-        <v>0.05630079</v>
+        <v>0.06243972</v>
       </c>
       <c r="N15">
-        <v>0.67169921</v>
+        <v>0.66556028</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>0.67169921</v>
+        <v>0.66556028</v>
       </c>
       <c r="Q15">
-        <v>1.13369921</v>
+        <v>1.12756028</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1056400748128763</v>
+        <v>0.1063358896362819</v>
       </c>
       <c r="T15">
-        <v>1.09599198516408</v>
+        <v>1.108736078014825</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0</v>
       </c>
       <c r="W15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>12.93054680049783</v>
+        <v>11.65924510872246</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0987008650872024</v>
+        <v>0.0987608650872024</v>
       </c>
       <c r="C16">
-        <v>7.391243269238157</v>
+        <v>7.304192828096117</v>
       </c>
       <c r="D16">
-        <v>3.766643269238156</v>
+        <v>3.765692828096117</v>
       </c>
       <c r="E16">
-        <v>1.2054</v>
+        <v>1.2915</v>
       </c>
       <c r="F16">
-        <v>1.2054</v>
+        <v>1.2915</v>
       </c>
       <c r="G16">
         <v>4.83</v>
@@ -2599,28 +2599,28 @@
         <v>0.728</v>
       </c>
       <c r="M16">
-        <v>0.06243972</v>
+        <v>0.06689970000000001</v>
       </c>
       <c r="N16">
-        <v>0.66556028</v>
+        <v>0.6611003</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>0.66556028</v>
+        <v>0.6611003</v>
       </c>
       <c r="Q16">
-        <v>1.12756028</v>
+        <v>1.1231003</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1063358896362819</v>
+        <v>0.1070480765731793</v>
       </c>
       <c r="T16">
-        <v>1.108736078014825</v>
+        <v>1.121780031873823</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.65924510872246</v>
+        <v>10.8819621014743</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0987608650872024</v>
+        <v>0.09882086508720241</v>
       </c>
       <c r="C17">
-        <v>7.304192828096117</v>
+        <v>7.217142866484747</v>
       </c>
       <c r="D17">
-        <v>3.765692828096117</v>
+        <v>3.764742866484747</v>
       </c>
       <c r="E17">
-        <v>1.2915</v>
+        <v>1.3776</v>
       </c>
       <c r="F17">
-        <v>1.2915</v>
+        <v>1.3776</v>
       </c>
       <c r="G17">
         <v>4.83</v>
@@ -2681,28 +2681,28 @@
         <v>0.728</v>
       </c>
       <c r="M17">
-        <v>0.06689969999999999</v>
+        <v>0.07135967999999999</v>
       </c>
       <c r="N17">
-        <v>0.6611003</v>
+        <v>0.6566403199999999</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>0.6611003</v>
+        <v>0.6566403199999999</v>
       </c>
       <c r="Q17">
-        <v>1.1231003</v>
+        <v>1.11864032</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1070480765731793</v>
+        <v>0.1077772203419076</v>
       </c>
       <c r="T17">
-        <v>1.121780031873823</v>
+        <v>1.135134556062797</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.8819621014743</v>
+        <v>10.20183947013215</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09882086508720241</v>
+        <v>0.09916986508720242</v>
       </c>
       <c r="C18">
-        <v>7.217142866484747</v>
+        <v>7.125526744488545</v>
       </c>
       <c r="D18">
-        <v>3.764742866484747</v>
+        <v>3.759226744488545</v>
       </c>
       <c r="E18">
-        <v>1.3776</v>
+        <v>1.4637</v>
       </c>
       <c r="F18">
-        <v>1.3776</v>
+        <v>1.4637</v>
       </c>
       <c r="G18">
         <v>4.83</v>
@@ -2763,45 +2763,45 @@
         <v>0.728</v>
       </c>
       <c r="M18">
-        <v>0.07135967999999999</v>
+        <v>0.07830795</v>
       </c>
       <c r="N18">
-        <v>0.6566403199999999</v>
+        <v>0.64969205</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>0.6566403199999999</v>
+        <v>0.64969205</v>
       </c>
       <c r="Q18">
-        <v>1.11864032</v>
+        <v>1.11169205</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1077772203419076</v>
+        <v>0.1085239338400029</v>
       </c>
       <c r="T18">
-        <v>1.135134556062797</v>
+        <v>1.148810876015361</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0</v>
       </c>
       <c r="W18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>10.20183947013215</v>
+        <v>9.296629524843901</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09916986508720242</v>
+        <v>0.0992468650872024</v>
       </c>
       <c r="C19">
-        <v>7.125526744488545</v>
+        <v>7.0382118963507</v>
       </c>
       <c r="D19">
-        <v>3.759226744488545</v>
+        <v>3.7580118963507</v>
       </c>
       <c r="E19">
-        <v>1.4637</v>
+        <v>1.5498</v>
       </c>
       <c r="F19">
-        <v>1.4637</v>
+        <v>1.5498</v>
       </c>
       <c r="G19">
         <v>4.83</v>
@@ -2845,28 +2845,28 @@
         <v>0.728</v>
       </c>
       <c r="M19">
-        <v>0.07830795</v>
+        <v>0.0829143</v>
       </c>
       <c r="N19">
-        <v>0.64969205</v>
+        <v>0.6450857</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>0.64969205</v>
+        <v>0.6450857</v>
       </c>
       <c r="Q19">
-        <v>1.11169205</v>
+        <v>1.1070857</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1085239338400029</v>
+        <v>0.109288859862442</v>
       </c>
       <c r="T19">
-        <v>1.148810876015361</v>
+        <v>1.162820764747255</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.296629524843901</v>
+        <v>8.780150106797018</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09924686508720242</v>
+        <v>0.09932386508720242</v>
       </c>
       <c r="C20">
-        <v>7.038211896350701</v>
+        <v>6.950897833150453</v>
       </c>
       <c r="D20">
-        <v>3.7580118963507</v>
+        <v>3.756797833150453</v>
       </c>
       <c r="E20">
-        <v>1.5498</v>
+        <v>1.6359</v>
       </c>
       <c r="F20">
-        <v>1.5498</v>
+        <v>1.6359</v>
       </c>
       <c r="G20">
         <v>4.83</v>
@@ -2927,28 +2927,28 @@
         <v>0.728</v>
       </c>
       <c r="M20">
-        <v>0.0829143</v>
+        <v>0.08752064999999999</v>
       </c>
       <c r="N20">
-        <v>0.6450857</v>
+        <v>0.64047935</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>0.6450857</v>
+        <v>0.64047935</v>
       </c>
       <c r="Q20">
-        <v>1.1070857</v>
+        <v>1.10247935</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.109288859862442</v>
+        <v>0.1100726729471635</v>
       </c>
       <c r="T20">
-        <v>1.162820764747255</v>
+        <v>1.177176576657715</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.780150106797018</v>
+        <v>8.318036943281387</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09932386508720242</v>
+        <v>0.09940086508720242</v>
       </c>
       <c r="C21">
-        <v>6.950897833150453</v>
+        <v>6.863584554127305</v>
       </c>
       <c r="D21">
-        <v>3.756797833150453</v>
+        <v>3.755584554127306</v>
       </c>
       <c r="E21">
-        <v>1.6359</v>
+        <v>1.722</v>
       </c>
       <c r="F21">
-        <v>1.6359</v>
+        <v>1.722</v>
       </c>
       <c r="G21">
         <v>4.83</v>
@@ -3009,28 +3009,28 @@
         <v>0.728</v>
       </c>
       <c r="M21">
-        <v>0.08752064999999999</v>
+        <v>0.092127</v>
       </c>
       <c r="N21">
-        <v>0.64047935</v>
+        <v>0.635873</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>0.64047935</v>
+        <v>0.635873</v>
       </c>
       <c r="Q21">
-        <v>1.10247935</v>
+        <v>1.097873</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1100726729471635</v>
+        <v>0.110876081359003</v>
       </c>
       <c r="T21">
-        <v>1.177176576657715</v>
+        <v>1.191891283865937</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.318036943281387</v>
+        <v>7.902135096117316</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09940086508720242</v>
+        <v>0.09964586508720241</v>
       </c>
       <c r="C22">
-        <v>6.863584554127305</v>
+        <v>6.773629329196078</v>
       </c>
       <c r="D22">
-        <v>3.755584554127306</v>
+        <v>3.751729329196078</v>
       </c>
       <c r="E22">
-        <v>1.722</v>
+        <v>1.8081</v>
       </c>
       <c r="F22">
-        <v>1.722</v>
+        <v>1.8081</v>
       </c>
       <c r="G22">
         <v>4.83</v>
@@ -3091,45 +3091,45 @@
         <v>0.728</v>
       </c>
       <c r="M22">
-        <v>0.092127</v>
+        <v>0.09817983000000001</v>
       </c>
       <c r="N22">
-        <v>0.635873</v>
+        <v>0.62982017</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>0.635873</v>
+        <v>0.62982017</v>
       </c>
       <c r="Q22">
-        <v>1.097873</v>
+        <v>1.09182017</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.110876081359003</v>
+        <v>0.1116998292243069</v>
       </c>
       <c r="T22">
-        <v>1.191891283865937</v>
+        <v>1.206978515307278</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0</v>
       </c>
       <c r="W22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.902135096117316</v>
+        <v>7.414964967855413</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09964586508720241</v>
+        <v>0.0997308650872024</v>
       </c>
       <c r="C23">
-        <v>6.773629329196078</v>
+        <v>6.686193650885555</v>
       </c>
       <c r="D23">
-        <v>3.751729329196078</v>
+        <v>3.750393650885555</v>
       </c>
       <c r="E23">
-        <v>1.8081</v>
+        <v>1.8942</v>
       </c>
       <c r="F23">
-        <v>1.8081</v>
+        <v>1.8942</v>
       </c>
       <c r="G23">
         <v>4.83</v>
@@ -3173,28 +3173,28 @@
         <v>0.728</v>
       </c>
       <c r="M23">
-        <v>0.09817983</v>
+        <v>0.10285506</v>
       </c>
       <c r="N23">
-        <v>0.62982017</v>
+        <v>0.62514494</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>0.62982017</v>
+        <v>0.62514494</v>
       </c>
       <c r="Q23">
-        <v>1.09182017</v>
+        <v>1.08714494</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1116998292243069</v>
+        <v>0.1125446988297467</v>
       </c>
       <c r="T23">
-        <v>1.206978515307278</v>
+        <v>1.222452598836858</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.414964967855414</v>
+        <v>7.077921105680168</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0997308650872024</v>
+        <v>0.09981586508720239</v>
       </c>
       <c r="C24">
-        <v>6.686193650885555</v>
+        <v>6.598758923284144</v>
       </c>
       <c r="D24">
-        <v>3.750393650885555</v>
+        <v>3.749058923284144</v>
       </c>
       <c r="E24">
-        <v>1.8942</v>
+        <v>1.9803</v>
       </c>
       <c r="F24">
-        <v>1.8942</v>
+        <v>1.9803</v>
       </c>
       <c r="G24">
         <v>4.83</v>
@@ -3255,28 +3255,28 @@
         <v>0.728</v>
       </c>
       <c r="M24">
-        <v>0.10285506</v>
+        <v>0.10753029</v>
       </c>
       <c r="N24">
-        <v>0.62514494</v>
+        <v>0.62046971</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>0.62514494</v>
+        <v>0.62046971</v>
       </c>
       <c r="Q24">
-        <v>1.08714494</v>
+        <v>1.08246971</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1125446988297467</v>
+        <v>0.1134115131002628</v>
       </c>
       <c r="T24">
-        <v>1.222452598836858</v>
+        <v>1.23832860661396</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.077921105680168</v>
+        <v>6.770185405433203</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09981586508720239</v>
+        <v>0.0999008650872024</v>
       </c>
       <c r="C25">
-        <v>6.598758923284144</v>
+        <v>6.511325145377162</v>
       </c>
       <c r="D25">
-        <v>3.749058923284144</v>
+        <v>3.747725145377161</v>
       </c>
       <c r="E25">
-        <v>1.9803</v>
+        <v>2.0664</v>
       </c>
       <c r="F25">
-        <v>1.9803</v>
+        <v>2.0664</v>
       </c>
       <c r="G25">
         <v>4.83</v>
@@ -3337,28 +3337,28 @@
         <v>0.728</v>
       </c>
       <c r="M25">
-        <v>0.10753029</v>
+        <v>0.11220552</v>
       </c>
       <c r="N25">
-        <v>0.62046971</v>
+        <v>0.6157944799999999</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>0.62046971</v>
+        <v>0.6157944799999999</v>
       </c>
       <c r="Q25">
-        <v>1.08246971</v>
+        <v>1.07779448</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1134115131002628</v>
+        <v>0.1143011382726347</v>
       </c>
       <c r="T25">
-        <v>1.23832860661396</v>
+        <v>1.254622404069407</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.770185405433203</v>
+        <v>6.488094346873486</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0999008650872024</v>
+        <v>0.09998586508720239</v>
       </c>
       <c r="C26">
-        <v>6.511325145377162</v>
+        <v>6.423892316151369</v>
       </c>
       <c r="D26">
-        <v>3.747725145377161</v>
+        <v>3.746392316151369</v>
       </c>
       <c r="E26">
-        <v>2.0664</v>
+        <v>2.1525</v>
       </c>
       <c r="F26">
-        <v>2.0664</v>
+        <v>2.1525</v>
       </c>
       <c r="G26">
         <v>4.83</v>
@@ -3419,28 +3419,28 @@
         <v>0.728</v>
       </c>
       <c r="M26">
-        <v>0.11220552</v>
+        <v>0.11688075</v>
       </c>
       <c r="N26">
-        <v>0.61579448</v>
+        <v>0.61111925</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>0.61579448</v>
+        <v>0.61111925</v>
       </c>
       <c r="Q26">
-        <v>1.07779448</v>
+        <v>1.07311925</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1143011382726347</v>
+        <v>0.1152144867829365</v>
       </c>
       <c r="T26">
-        <v>1.254622404069407</v>
+        <v>1.271350702790332</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.488094346873488</v>
+        <v>6.228570572998548</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09998586508720239</v>
+        <v>0.1003308650872024</v>
       </c>
       <c r="C27">
-        <v>6.423892316151369</v>
+        <v>6.332392316147731</v>
       </c>
       <c r="D27">
-        <v>3.746392316151369</v>
+        <v>3.74099231614773</v>
       </c>
       <c r="E27">
-        <v>2.1525</v>
+        <v>2.2386</v>
       </c>
       <c r="F27">
-        <v>2.1525</v>
+        <v>2.2386</v>
       </c>
       <c r="G27">
         <v>4.83</v>
@@ -3501,45 +3501,45 @@
         <v>0.728</v>
       </c>
       <c r="M27">
-        <v>0.11688075</v>
+        <v>0.12379458</v>
       </c>
       <c r="N27">
-        <v>0.61111925</v>
+        <v>0.60420542</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>0.61111925</v>
+        <v>0.60420542</v>
       </c>
       <c r="Q27">
-        <v>1.07311925</v>
+        <v>1.06620542</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1152144867829365</v>
+        <v>0.1161525203881114</v>
       </c>
       <c r="T27">
-        <v>1.271350702790332</v>
+        <v>1.288531117692904</v>
       </c>
       <c r="U27">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V27">
         <v>0</v>
       </c>
       <c r="W27">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.228570572998548</v>
+        <v>5.880709801673062</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1003308650872024</v>
+        <v>0.1004258650872024</v>
       </c>
       <c r="C28">
-        <v>6.332392316147731</v>
+        <v>6.2448080919982</v>
       </c>
       <c r="D28">
-        <v>3.74099231614773</v>
+        <v>3.7395080919982</v>
       </c>
       <c r="E28">
-        <v>2.2386</v>
+        <v>2.3247</v>
       </c>
       <c r="F28">
-        <v>2.2386</v>
+        <v>2.3247</v>
       </c>
       <c r="G28">
         <v>4.83</v>
@@ -3583,28 +3583,28 @@
         <v>0.728</v>
       </c>
       <c r="M28">
-        <v>0.12379458</v>
+        <v>0.12855591</v>
       </c>
       <c r="N28">
-        <v>0.60420542</v>
+        <v>0.59944409</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>0.60420542</v>
+        <v>0.59944409</v>
       </c>
       <c r="Q28">
-        <v>1.06620542</v>
+        <v>1.06144409</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1161525203881114</v>
+        <v>0.1171162535441129</v>
       </c>
       <c r="T28">
-        <v>1.288531117692904</v>
+        <v>1.306182228894177</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.880709801673062</v>
+        <v>5.66290573494443</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1004258650872024</v>
+        <v>0.1005208650872024</v>
       </c>
       <c r="C29">
-        <v>6.2448080919982</v>
+        <v>6.157225045101917</v>
       </c>
       <c r="D29">
-        <v>3.7395080919982</v>
+        <v>3.738025045101918</v>
       </c>
       <c r="E29">
-        <v>2.3247</v>
+        <v>2.4108</v>
       </c>
       <c r="F29">
-        <v>2.3247</v>
+        <v>2.4108</v>
       </c>
       <c r="G29">
         <v>4.83</v>
@@ -3665,28 +3665,28 @@
         <v>0.728</v>
       </c>
       <c r="M29">
-        <v>0.12855591</v>
+        <v>0.13331724</v>
       </c>
       <c r="N29">
-        <v>0.59944409</v>
+        <v>0.59468276</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>0.59944409</v>
+        <v>0.59468276</v>
       </c>
       <c r="Q29">
-        <v>1.06144409</v>
+        <v>1.05668276</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1171162535441129</v>
+        <v>0.1181067570655589</v>
       </c>
       <c r="T29">
-        <v>1.306182228894177</v>
+        <v>1.324323648739929</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.66290573494443</v>
+        <v>5.460659101553557</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1005208650872024</v>
+        <v>0.1006158650872024</v>
       </c>
       <c r="C30">
-        <v>6.157225045101917</v>
+        <v>6.069643174058779</v>
       </c>
       <c r="D30">
-        <v>3.738025045101918</v>
+        <v>3.736543174058778</v>
       </c>
       <c r="E30">
-        <v>2.4108</v>
+        <v>2.4969</v>
       </c>
       <c r="F30">
-        <v>2.4108</v>
+        <v>2.4969</v>
       </c>
       <c r="G30">
         <v>4.83</v>
@@ -3747,28 +3747,28 @@
         <v>0.728</v>
       </c>
       <c r="M30">
-        <v>0.13331724</v>
+        <v>0.13807857</v>
       </c>
       <c r="N30">
-        <v>0.59468276</v>
+        <v>0.58992143</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>0.59468276</v>
+        <v>0.58992143</v>
       </c>
       <c r="Q30">
-        <v>1.05668276</v>
+        <v>1.05192143</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1181067570655589</v>
+        <v>0.1191251620946513</v>
       </c>
       <c r="T30">
-        <v>1.324323648739929</v>
+        <v>1.34297609449683</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.460659101553557</v>
+        <v>5.272360511844814</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1006158650872024</v>
+        <v>0.1007108650872024</v>
       </c>
       <c r="C31">
-        <v>6.069643174058779</v>
+        <v>5.982062477470901</v>
       </c>
       <c r="D31">
-        <v>3.736543174058778</v>
+        <v>3.735062477470902</v>
       </c>
       <c r="E31">
-        <v>2.4969</v>
+        <v>2.583</v>
       </c>
       <c r="F31">
-        <v>2.4969</v>
+        <v>2.583</v>
       </c>
       <c r="G31">
         <v>4.83</v>
@@ -3829,28 +3829,28 @@
         <v>0.728</v>
       </c>
       <c r="M31">
-        <v>0.13807857</v>
+        <v>0.1428399</v>
       </c>
       <c r="N31">
-        <v>0.58992143</v>
+        <v>0.5851601</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>0.58992143</v>
+        <v>0.5851601</v>
       </c>
       <c r="Q31">
-        <v>1.05192143</v>
+        <v>1.0471601</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1191251620946513</v>
+        <v>0.1201726644102891</v>
       </c>
       <c r="T31">
-        <v>1.34297609449683</v>
+        <v>1.362161467275356</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.272360511844814</v>
+        <v>5.096615161449987</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1007108650872024</v>
+        <v>0.1008058650872024</v>
       </c>
       <c r="C32">
-        <v>5.982062477470901</v>
+        <v>5.894482953942621</v>
       </c>
       <c r="D32">
-        <v>3.735062477470902</v>
+        <v>3.733582953942621</v>
       </c>
       <c r="E32">
-        <v>2.583</v>
+        <v>2.6691</v>
       </c>
       <c r="F32">
-        <v>2.583</v>
+        <v>2.6691</v>
       </c>
       <c r="G32">
         <v>4.83</v>
@@ -3911,28 +3911,28 @@
         <v>0.728</v>
       </c>
       <c r="M32">
-        <v>0.1428399</v>
+        <v>0.14760123</v>
       </c>
       <c r="N32">
-        <v>0.5851601</v>
+        <v>0.58039877</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>0.5851601</v>
+        <v>0.58039877</v>
       </c>
       <c r="Q32">
-        <v>1.0471601</v>
+        <v>1.04239877</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1201726644102891</v>
+        <v>0.1212505291118876</v>
       </c>
       <c r="T32">
-        <v>1.362161467275356</v>
+        <v>1.381902937815579</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.096615161449987</v>
+        <v>4.932208220758051</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1008058650872024</v>
+        <v>0.1009008650872024</v>
       </c>
       <c r="C33">
-        <v>5.894482953942621</v>
+        <v>5.806904602080479</v>
       </c>
       <c r="D33">
-        <v>3.733582953942621</v>
+        <v>3.732104602080479</v>
       </c>
       <c r="E33">
-        <v>2.6691</v>
+        <v>2.7552</v>
       </c>
       <c r="F33">
-        <v>2.6691</v>
+        <v>2.7552</v>
       </c>
       <c r="G33">
         <v>4.83</v>
@@ -3993,28 +3993,28 @@
         <v>0.728</v>
       </c>
       <c r="M33">
-        <v>0.14760123</v>
+        <v>0.15236256</v>
       </c>
       <c r="N33">
-        <v>0.58039877</v>
+        <v>0.5756374399999999</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>0.58039877</v>
+        <v>0.5756374399999999</v>
       </c>
       <c r="Q33">
-        <v>1.04239877</v>
+        <v>1.03763744</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1212505291118876</v>
+        <v>0.1223600957164741</v>
       </c>
       <c r="T33">
-        <v>1.381902937815579</v>
+        <v>1.402225039842278</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.932208220758051</v>
+        <v>4.778076713859362</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1009008650872024</v>
+        <v>0.1009958650872024</v>
       </c>
       <c r="C34">
-        <v>5.806904602080479</v>
+        <v>5.719327420493226</v>
       </c>
       <c r="D34">
-        <v>3.732104602080479</v>
+        <v>3.730627420493227</v>
       </c>
       <c r="E34">
-        <v>2.7552</v>
+        <v>2.8413</v>
       </c>
       <c r="F34">
-        <v>2.7552</v>
+        <v>2.8413</v>
       </c>
       <c r="G34">
         <v>4.83</v>
@@ -4075,28 +4075,28 @@
         <v>0.728</v>
       </c>
       <c r="M34">
-        <v>0.15236256</v>
+        <v>0.15712389</v>
       </c>
       <c r="N34">
-        <v>0.5756374399999999</v>
+        <v>0.5708761099999999</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>0.5756374399999999</v>
+        <v>0.5708761099999999</v>
       </c>
       <c r="Q34">
-        <v>1.03763744</v>
+        <v>1.03287611</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1223600957164741</v>
+        <v>0.1235027837122424</v>
       </c>
       <c r="T34">
-        <v>1.402225039842278</v>
+        <v>1.423153771780223</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.778076713859362</v>
+        <v>4.633286510409079</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1009958650872024</v>
+        <v>0.1019408650872024</v>
       </c>
       <c r="C35">
-        <v>5.719327420493226</v>
+        <v>5.618596770890539</v>
       </c>
       <c r="D35">
-        <v>3.730627420493227</v>
+        <v>3.71599677089054</v>
       </c>
       <c r="E35">
-        <v>2.8413</v>
+        <v>2.9274</v>
       </c>
       <c r="F35">
-        <v>2.8413</v>
+        <v>2.9274</v>
       </c>
       <c r="G35">
         <v>4.83</v>
@@ -4157,45 +4157,45 @@
         <v>0.728</v>
       </c>
       <c r="M35">
-        <v>0.15712389</v>
+        <v>0.16920372</v>
       </c>
       <c r="N35">
-        <v>0.5708761099999999</v>
+        <v>0.5587962799999999</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>0.5708761099999999</v>
+        <v>0.5587962799999999</v>
       </c>
       <c r="Q35">
-        <v>1.03287611</v>
+        <v>1.02079628</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1235027837122424</v>
+        <v>0.1246800986169733</v>
       </c>
       <c r="T35">
-        <v>1.423153771780223</v>
+        <v>1.444716707716287</v>
       </c>
       <c r="U35">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V35">
         <v>0</v>
       </c>
       <c r="W35">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.633286510409079</v>
+        <v>4.302505878712359</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1019408650872024</v>
+        <v>0.1020608650872024</v>
       </c>
       <c r="C36">
-        <v>5.618596770890539</v>
+        <v>5.530647117848757</v>
       </c>
       <c r="D36">
-        <v>3.71599677089054</v>
+        <v>3.714147117848757</v>
       </c>
       <c r="E36">
-        <v>2.9274</v>
+        <v>3.0135</v>
       </c>
       <c r="F36">
-        <v>2.9274</v>
+        <v>3.0135</v>
       </c>
       <c r="G36">
         <v>4.83</v>
@@ -4239,28 +4239,28 @@
         <v>0.728</v>
       </c>
       <c r="M36">
-        <v>0.16920372</v>
+        <v>0.1741803</v>
       </c>
       <c r="N36">
-        <v>0.5587962799999999</v>
+        <v>0.5538197</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>0.5587962799999999</v>
+        <v>0.5538197</v>
       </c>
       <c r="Q36">
-        <v>1.02079628</v>
+        <v>1.0158197</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1246800986169733</v>
+        <v>0.125893638595696</v>
       </c>
       <c r="T36">
-        <v>1.444716707716287</v>
+        <v>1.46694311860423</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.302505878712359</v>
+        <v>4.179577139320577</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1020608650872024</v>
+        <v>0.1021808650872024</v>
       </c>
       <c r="C37">
-        <v>5.530647117848757</v>
+        <v>5.442699305236074</v>
       </c>
       <c r="D37">
-        <v>3.714147117848757</v>
+        <v>3.712299305236075</v>
       </c>
       <c r="E37">
-        <v>3.0135</v>
+        <v>3.0996</v>
       </c>
       <c r="F37">
-        <v>3.0135</v>
+        <v>3.0996</v>
       </c>
       <c r="G37">
         <v>4.83</v>
@@ -4321,28 +4321,28 @@
         <v>0.728</v>
       </c>
       <c r="M37">
-        <v>0.1741803</v>
+        <v>0.17915688</v>
       </c>
       <c r="N37">
-        <v>0.5538197</v>
+        <v>0.5488431199999999</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>0.5538197</v>
+        <v>0.5488431199999999</v>
       </c>
       <c r="Q37">
-        <v>1.0158197</v>
+        <v>1.01084312</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.125893638595696</v>
+        <v>0.1271451016987538</v>
       </c>
       <c r="T37">
-        <v>1.46694311860423</v>
+        <v>1.489864104832421</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.179577139320577</v>
+        <v>4.06347777433945</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1021808650872024</v>
+        <v>0.1035958650872024</v>
       </c>
       <c r="C38">
-        <v>5.442699305236075</v>
+        <v>5.334948368652065</v>
       </c>
       <c r="D38">
-        <v>3.712299305236074</v>
+        <v>3.690648368652066</v>
       </c>
       <c r="E38">
-        <v>3.0996</v>
+        <v>3.1857</v>
       </c>
       <c r="F38">
-        <v>3.0996</v>
+        <v>3.1857</v>
       </c>
       <c r="G38">
         <v>4.83</v>
@@ -4403,45 +4403,45 @@
         <v>0.728</v>
       </c>
       <c r="M38">
-        <v>0.17915688</v>
+        <v>0.19528341</v>
       </c>
       <c r="N38">
-        <v>0.54884312</v>
+        <v>0.5327165899999999</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>0.54884312</v>
+        <v>0.5327165899999999</v>
       </c>
       <c r="Q38">
-        <v>1.01084312</v>
+        <v>0.9947165899999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1271451016987538</v>
+        <v>0.1284362937892102</v>
       </c>
       <c r="T38">
-        <v>1.489864104832421</v>
+        <v>1.513512741417063</v>
       </c>
       <c r="U38">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V38">
         <v>0</v>
       </c>
       <c r="W38">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.06347777433945</v>
+        <v>3.727915238677981</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1035958650872024</v>
+        <v>0.1037508650872024</v>
       </c>
       <c r="C39">
-        <v>5.334948368652065</v>
+        <v>5.246492048678971</v>
       </c>
       <c r="D39">
-        <v>3.690648368652066</v>
+        <v>3.688292048678971</v>
       </c>
       <c r="E39">
-        <v>3.1857</v>
+        <v>3.2718</v>
       </c>
       <c r="F39">
-        <v>3.1857</v>
+        <v>3.2718</v>
       </c>
       <c r="G39">
         <v>4.83</v>
@@ -4485,28 +4485,28 @@
         <v>0.728</v>
       </c>
       <c r="M39">
-        <v>0.19528341</v>
+        <v>0.20056134</v>
       </c>
       <c r="N39">
-        <v>0.5327165899999999</v>
+        <v>0.5274386600000001</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>0.5327165899999999</v>
+        <v>0.5274386600000001</v>
       </c>
       <c r="Q39">
-        <v>0.9947165899999999</v>
+        <v>0.98943866</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1284362937892102</v>
+        <v>0.1297691372374232</v>
       </c>
       <c r="T39">
-        <v>1.513512741417063</v>
+        <v>1.53792423724637</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.727915238677981</v>
+        <v>3.629812206081192</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1037508650872024</v>
+        <v>0.1039058650872024</v>
       </c>
       <c r="C40">
-        <v>5.246492048678971</v>
+        <v>5.158038735603665</v>
       </c>
       <c r="D40">
-        <v>3.688292048678971</v>
+        <v>3.685938735603664</v>
       </c>
       <c r="E40">
-        <v>3.2718</v>
+        <v>3.3579</v>
       </c>
       <c r="F40">
-        <v>3.2718</v>
+        <v>3.3579</v>
       </c>
       <c r="G40">
         <v>4.83</v>
@@ -4567,28 +4567,28 @@
         <v>0.728</v>
       </c>
       <c r="M40">
-        <v>0.20056134</v>
+        <v>0.20583927</v>
       </c>
       <c r="N40">
-        <v>0.5274386600000001</v>
+        <v>0.52216073</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>0.5274386600000001</v>
+        <v>0.52216073</v>
       </c>
       <c r="Q40">
-        <v>0.98943866</v>
+        <v>0.9841607299999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1297691372374232</v>
+        <v>0.1311456804708236</v>
       </c>
       <c r="T40">
-        <v>1.53792423724637</v>
+        <v>1.563136109988114</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.629812206081192</v>
+        <v>3.536740098232956</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1039058650872024</v>
+        <v>0.1051808650872024</v>
       </c>
       <c r="C41">
-        <v>5.158038735603665</v>
+        <v>5.052694193466432</v>
       </c>
       <c r="D41">
-        <v>3.685938735603664</v>
+        <v>3.666694193466431</v>
       </c>
       <c r="E41">
-        <v>3.3579</v>
+        <v>3.444</v>
       </c>
       <c r="F41">
-        <v>3.3579</v>
+        <v>3.444</v>
       </c>
       <c r="G41">
         <v>4.83</v>
@@ -4649,45 +4649,45 @@
         <v>0.728</v>
       </c>
       <c r="M41">
-        <v>0.20583927</v>
+        <v>0.2207604</v>
       </c>
       <c r="N41">
-        <v>0.52216073</v>
+        <v>0.5072395999999999</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>0.52216073</v>
+        <v>0.5072395999999999</v>
       </c>
       <c r="Q41">
-        <v>0.9841607299999999</v>
+        <v>0.9692395999999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1311456804708236</v>
+        <v>0.1325681084786707</v>
       </c>
       <c r="T41">
-        <v>1.563136109988114</v>
+        <v>1.589188378487915</v>
       </c>
       <c r="U41">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V41">
         <v>0</v>
       </c>
       <c r="W41">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.536740098232956</v>
+        <v>3.297692883325088</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1051808650872024</v>
+        <v>0.1053638650872024</v>
       </c>
       <c r="C42">
-        <v>5.052694193466432</v>
+        <v>4.963848514620225</v>
       </c>
       <c r="D42">
-        <v>3.666694193466431</v>
+        <v>3.663948514620225</v>
       </c>
       <c r="E42">
-        <v>3.444</v>
+        <v>3.5301</v>
       </c>
       <c r="F42">
-        <v>3.444</v>
+        <v>3.5301</v>
       </c>
       <c r="G42">
         <v>4.83</v>
@@ -4731,28 +4731,28 @@
         <v>0.728</v>
       </c>
       <c r="M42">
-        <v>0.2207604</v>
+        <v>0.22627941</v>
       </c>
       <c r="N42">
-        <v>0.5072395999999999</v>
+        <v>0.5017205899999999</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>0.5072395999999999</v>
+        <v>0.5017205899999999</v>
       </c>
       <c r="Q42">
-        <v>0.9692395999999999</v>
+        <v>0.9637205899999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1325681084786707</v>
+        <v>0.1340387543850888</v>
       </c>
       <c r="T42">
-        <v>1.589188378487915</v>
+        <v>1.616123774733473</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.297692883325088</v>
+        <v>3.217261349585452</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1053638650872024</v>
+        <v>0.1055468650872024</v>
       </c>
       <c r="C43">
-        <v>4.963848514620225</v>
+        <v>4.875006944713031</v>
       </c>
       <c r="D43">
-        <v>3.663948514620225</v>
+        <v>3.661206944713032</v>
       </c>
       <c r="E43">
-        <v>3.5301</v>
+        <v>3.6162</v>
       </c>
       <c r="F43">
-        <v>3.5301</v>
+        <v>3.6162</v>
       </c>
       <c r="G43">
         <v>4.83</v>
@@ -4813,28 +4813,28 @@
         <v>0.728</v>
       </c>
       <c r="M43">
-        <v>0.22627941</v>
+        <v>0.23179842</v>
       </c>
       <c r="N43">
-        <v>0.5017205899999999</v>
+        <v>0.4962015799999999</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>0.5017205899999999</v>
+        <v>0.4962015799999999</v>
       </c>
       <c r="Q43">
-        <v>0.9637205899999999</v>
+        <v>0.9582015799999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1340387543850888</v>
+        <v>0.1355601122193145</v>
       </c>
       <c r="T43">
-        <v>1.616123774733473</v>
+        <v>1.64398797774612</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.217261349585452</v>
+        <v>3.140659888881037</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1055468650872024</v>
+        <v>0.1057298650872024</v>
       </c>
       <c r="C44">
-        <v>4.875006944713032</v>
+        <v>4.786169474528142</v>
       </c>
       <c r="D44">
-        <v>3.661206944713032</v>
+        <v>3.658469474528141</v>
       </c>
       <c r="E44">
-        <v>3.6162</v>
+        <v>3.7023</v>
       </c>
       <c r="F44">
-        <v>3.6162</v>
+        <v>3.7023</v>
       </c>
       <c r="G44">
         <v>4.83</v>
@@ -4895,28 +4895,28 @@
         <v>0.728</v>
       </c>
       <c r="M44">
-        <v>0.23179842</v>
+        <v>0.23731743</v>
       </c>
       <c r="N44">
-        <v>0.49620158</v>
+        <v>0.49068257</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>0.49620158</v>
+        <v>0.49068257</v>
       </c>
       <c r="Q44">
-        <v>0.95820158</v>
+        <v>0.95268257</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1355601122193145</v>
+        <v>0.1371348510301796</v>
       </c>
       <c r="T44">
-        <v>1.643987977746119</v>
+        <v>1.672829872092543</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.140659888881037</v>
+        <v>3.067621286814036</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1057298650872024</v>
+        <v>0.1093448650872024</v>
       </c>
       <c r="C45">
-        <v>4.786169474528142</v>
+        <v>4.646820147725483</v>
       </c>
       <c r="D45">
-        <v>3.658469474528141</v>
+        <v>3.605220147725483</v>
       </c>
       <c r="E45">
-        <v>3.7023</v>
+        <v>3.7884</v>
       </c>
       <c r="F45">
-        <v>3.7023</v>
+        <v>3.7884</v>
       </c>
       <c r="G45">
         <v>4.83</v>
@@ -4977,45 +4977,45 @@
         <v>0.728</v>
       </c>
       <c r="M45">
-        <v>0.23731743</v>
+        <v>0.27238596</v>
       </c>
       <c r="N45">
-        <v>0.49068257</v>
+        <v>0.45561404</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>0.49068257</v>
+        <v>0.45561404</v>
       </c>
       <c r="Q45">
-        <v>0.95268257</v>
+        <v>0.91761404</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1371348510301796</v>
+        <v>0.1387658305128614</v>
       </c>
       <c r="T45">
-        <v>1.672829872092543</v>
+        <v>1.702701834094195</v>
       </c>
       <c r="U45">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V45">
         <v>0</v>
       </c>
       <c r="W45">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.067621286814036</v>
+        <v>2.672678136567685</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1093448650872024</v>
+        <v>0.1096058650872024</v>
       </c>
       <c r="C46">
-        <v>4.646820147725483</v>
+        <v>4.556935525496511</v>
       </c>
       <c r="D46">
-        <v>3.605220147725483</v>
+        <v>3.601435525496512</v>
       </c>
       <c r="E46">
-        <v>3.7884</v>
+        <v>3.8745</v>
       </c>
       <c r="F46">
-        <v>3.7884</v>
+        <v>3.8745</v>
       </c>
       <c r="G46">
         <v>4.83</v>
@@ -5059,28 +5059,28 @@
         <v>0.728</v>
       </c>
       <c r="M46">
-        <v>0.27238596</v>
+        <v>0.27857655</v>
       </c>
       <c r="N46">
-        <v>0.45561404</v>
+        <v>0.4494234499999999</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>0.45561404</v>
+        <v>0.4494234499999999</v>
       </c>
       <c r="Q46">
-        <v>0.91761404</v>
+        <v>0.91142345</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1387658305128614</v>
+        <v>0.140456118340368</v>
       </c>
       <c r="T46">
-        <v>1.702701834094195</v>
+        <v>1.733660049259544</v>
       </c>
       <c r="U46">
         <v>0.07190000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.672678136567685</v>
+        <v>2.613285289088403</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1096058650872024</v>
+        <v>0.1098668650872024</v>
       </c>
       <c r="C47">
-        <v>4.556935525496511</v>
+        <v>4.467058840838328</v>
       </c>
       <c r="D47">
-        <v>3.601435525496512</v>
+        <v>3.597658840838327</v>
       </c>
       <c r="E47">
-        <v>3.8745</v>
+        <v>3.9606</v>
       </c>
       <c r="F47">
-        <v>3.8745</v>
+        <v>3.9606</v>
       </c>
       <c r="G47">
         <v>4.83</v>
@@ -5141,28 +5141,28 @@
         <v>0.728</v>
       </c>
       <c r="M47">
-        <v>0.27857655</v>
+        <v>0.28476714</v>
       </c>
       <c r="N47">
-        <v>0.4494234499999999</v>
+        <v>0.44323286</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>0.4494234499999999</v>
+        <v>0.44323286</v>
       </c>
       <c r="Q47">
-        <v>0.91142345</v>
+        <v>0.9052328599999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.140456118340368</v>
+        <v>0.1422090094207452</v>
       </c>
       <c r="T47">
-        <v>1.733660049259544</v>
+        <v>1.765764864986573</v>
       </c>
       <c r="U47">
         <v>0.07190000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.613285289088403</v>
+        <v>2.556474739325612</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1098668650872024</v>
+        <v>0.1101278650872024</v>
       </c>
       <c r="C48">
-        <v>4.467058840838328</v>
+        <v>4.377190068805629</v>
       </c>
       <c r="D48">
-        <v>3.597658840838327</v>
+        <v>3.593890068805629</v>
       </c>
       <c r="E48">
-        <v>3.9606</v>
+        <v>4.0467</v>
       </c>
       <c r="F48">
-        <v>3.9606</v>
+        <v>4.0467</v>
       </c>
       <c r="G48">
         <v>4.83</v>
@@ -5223,28 +5223,28 @@
         <v>0.728</v>
       </c>
       <c r="M48">
-        <v>0.28476714</v>
+        <v>0.29095773</v>
       </c>
       <c r="N48">
-        <v>0.44323286</v>
+        <v>0.43704227</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>0.44323286</v>
+        <v>0.43704227</v>
       </c>
       <c r="Q48">
-        <v>0.9052328599999999</v>
+        <v>0.89904227</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1422090094207452</v>
+        <v>0.1440280473343442</v>
       </c>
       <c r="T48">
-        <v>1.765764864986573</v>
+        <v>1.799081183193867</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.556474739325612</v>
+        <v>2.502081659765492</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1101278650872024</v>
+        <v>0.1122608650872024</v>
       </c>
       <c r="C49">
-        <v>4.377190068805629</v>
+        <v>4.260583539001071</v>
       </c>
       <c r="D49">
-        <v>3.593890068805629</v>
+        <v>3.563383539001072</v>
       </c>
       <c r="E49">
-        <v>4.0467</v>
+        <v>4.1328</v>
       </c>
       <c r="F49">
-        <v>4.0467</v>
+        <v>4.1328</v>
       </c>
       <c r="G49">
         <v>4.83</v>
@@ -5305,45 +5305,45 @@
         <v>0.728</v>
       </c>
       <c r="M49">
-        <v>0.29095773</v>
+        <v>0.3132662400000001</v>
       </c>
       <c r="N49">
-        <v>0.43704227</v>
+        <v>0.4147337599999999</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>0.43704227</v>
+        <v>0.4147337599999999</v>
       </c>
       <c r="Q49">
-        <v>0.89904227</v>
+        <v>0.8767337599999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1440280473343442</v>
+        <v>0.14591704824462</v>
       </c>
       <c r="T49">
-        <v>1.799081183193867</v>
+        <v>1.833678898255287</v>
       </c>
       <c r="U49">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V49">
         <v>0</v>
       </c>
       <c r="W49">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.502081659765492</v>
+        <v>2.323901866987007</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1122608650872024</v>
+        <v>0.1125608650872024</v>
       </c>
       <c r="C50">
-        <v>4.260583539001074</v>
+        <v>4.170234381737011</v>
       </c>
       <c r="D50">
-        <v>3.563383539001073</v>
+        <v>3.55913438173701</v>
       </c>
       <c r="E50">
-        <v>4.1328</v>
+        <v>4.2189</v>
       </c>
       <c r="F50">
-        <v>4.1328</v>
+        <v>4.2189</v>
       </c>
       <c r="G50">
         <v>4.83</v>
@@ -5387,28 +5387,28 @@
         <v>0.728</v>
       </c>
       <c r="M50">
-        <v>0.31326624</v>
+        <v>0.31979262</v>
       </c>
       <c r="N50">
-        <v>0.41473376</v>
+        <v>0.40820738</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>0.41473376</v>
+        <v>0.40820738</v>
       </c>
       <c r="Q50">
-        <v>0.87673376</v>
+        <v>0.87020738</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.14591704824462</v>
+        <v>0.1478801276219655</v>
       </c>
       <c r="T50">
-        <v>1.833678898255287</v>
+        <v>1.869633386456371</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.323901866987008</v>
+        <v>2.276475298272987</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1125608650872024</v>
+        <v>0.1128608650872024</v>
       </c>
       <c r="C51">
-        <v>4.170234381737011</v>
+        <v>4.079895346219772</v>
       </c>
       <c r="D51">
-        <v>3.55913438173701</v>
+        <v>3.554895346219771</v>
       </c>
       <c r="E51">
-        <v>4.2189</v>
+        <v>4.305</v>
       </c>
       <c r="F51">
-        <v>4.2189</v>
+        <v>4.305</v>
       </c>
       <c r="G51">
         <v>4.83</v>
@@ -5469,28 +5469,28 @@
         <v>0.728</v>
       </c>
       <c r="M51">
-        <v>0.31979262</v>
+        <v>0.326319</v>
       </c>
       <c r="N51">
-        <v>0.40820738</v>
+        <v>0.401681</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>0.40820738</v>
+        <v>0.401681</v>
       </c>
       <c r="Q51">
-        <v>0.87020738</v>
+        <v>0.8636809999999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1478801276219655</v>
+        <v>0.1499217301744048</v>
       </c>
       <c r="T51">
-        <v>1.869633386456371</v>
+        <v>1.907026054185499</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.276475298272987</v>
+        <v>2.230945792307527</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1128608650872024</v>
+        <v>0.1131608650872024</v>
       </c>
       <c r="C52">
-        <v>4.079895346219772</v>
+        <v>3.989566396326468</v>
       </c>
       <c r="D52">
-        <v>3.554895346219771</v>
+        <v>3.550666396326469</v>
       </c>
       <c r="E52">
-        <v>4.305</v>
+        <v>4.3911</v>
       </c>
       <c r="F52">
-        <v>4.305</v>
+        <v>4.3911</v>
       </c>
       <c r="G52">
         <v>4.83</v>
@@ -5551,28 +5551,28 @@
         <v>0.728</v>
       </c>
       <c r="M52">
-        <v>0.326319</v>
+        <v>0.33284538</v>
       </c>
       <c r="N52">
-        <v>0.401681</v>
+        <v>0.39515462</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>0.401681</v>
+        <v>0.39515462</v>
       </c>
       <c r="Q52">
-        <v>0.8636809999999999</v>
+        <v>0.85715462</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1499217301744048</v>
+        <v>0.1520466634432702</v>
       </c>
       <c r="T52">
-        <v>1.907026054185499</v>
+        <v>1.945944953250509</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.230945792307527</v>
+        <v>2.187201757164242</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1131608650872024</v>
+        <v>0.1134608650872024</v>
       </c>
       <c r="C53">
-        <v>3.989566396326468</v>
+        <v>3.899247496105902</v>
       </c>
       <c r="D53">
-        <v>3.550666396326469</v>
+        <v>3.546447496105901</v>
       </c>
       <c r="E53">
-        <v>4.3911</v>
+        <v>4.4772</v>
       </c>
       <c r="F53">
-        <v>4.3911</v>
+        <v>4.4772</v>
       </c>
       <c r="G53">
         <v>4.83</v>
@@ -5633,28 +5633,28 @@
         <v>0.728</v>
       </c>
       <c r="M53">
-        <v>0.33284538</v>
+        <v>0.33937176</v>
       </c>
       <c r="N53">
-        <v>0.39515462</v>
+        <v>0.38862824</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
       <c r="P53">
-        <v>0.39515462</v>
+        <v>0.38862824</v>
       </c>
       <c r="Q53">
-        <v>0.85715462</v>
+        <v>0.85062824</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1520466634432702</v>
+        <v>0.1542601355983383</v>
       </c>
       <c r="T53">
-        <v>1.945944953250509</v>
+        <v>1.986485473109895</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.187201757164242</v>
+        <v>2.145140184911084</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1134608650872024</v>
+        <v>0.1137608650872024</v>
       </c>
       <c r="C54">
-        <v>3.899247496105902</v>
+        <v>3.808938609777535</v>
       </c>
       <c r="D54">
-        <v>3.546447496105901</v>
+        <v>3.542238609777534</v>
       </c>
       <c r="E54">
-        <v>4.4772</v>
+        <v>4.5633</v>
       </c>
       <c r="F54">
-        <v>4.4772</v>
+        <v>4.5633</v>
       </c>
       <c r="G54">
         <v>4.83</v>
@@ -5715,28 +5715,28 @@
         <v>0.728</v>
       </c>
       <c r="M54">
-        <v>0.33937176</v>
+        <v>0.34589814</v>
       </c>
       <c r="N54">
-        <v>0.38862824</v>
+        <v>0.38210186</v>
       </c>
       <c r="O54">
         <v>0</v>
       </c>
       <c r="P54">
-        <v>0.38862824</v>
+        <v>0.38210186</v>
       </c>
       <c r="Q54">
-        <v>0.85062824</v>
+        <v>0.84410186</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1542601355983383</v>
+        <v>0.1565677980578775</v>
       </c>
       <c r="T54">
-        <v>1.986485473109895</v>
+        <v>2.028751121473935</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.145140184911084</v>
+        <v>2.104665841799554</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1137608650872024</v>
+        <v>0.1140608650872024</v>
       </c>
       <c r="C55">
-        <v>3.808938609777535</v>
+        <v>3.718639701730485</v>
       </c>
       <c r="D55">
-        <v>3.542238609777534</v>
+        <v>3.538039701730486</v>
       </c>
       <c r="E55">
-        <v>4.5633</v>
+        <v>4.6494</v>
       </c>
       <c r="F55">
-        <v>4.5633</v>
+        <v>4.6494</v>
       </c>
       <c r="G55">
         <v>4.83</v>
@@ -5797,28 +5797,28 @@
         <v>0.728</v>
       </c>
       <c r="M55">
-        <v>0.34589814</v>
+        <v>0.35242452</v>
       </c>
       <c r="N55">
-        <v>0.38210186</v>
+        <v>0.37557548</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
       <c r="P55">
-        <v>0.38210186</v>
+        <v>0.37557548</v>
       </c>
       <c r="Q55">
-        <v>0.84410186</v>
+        <v>0.8375754799999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1565677980578775</v>
+        <v>0.1589757936678313</v>
       </c>
       <c r="T55">
-        <v>2.028751121473935</v>
+        <v>2.072854406723368</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.104665841799554</v>
+        <v>2.065690548432896</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1140608650872024</v>
+        <v>0.1143608650872024</v>
       </c>
       <c r="C56">
-        <v>3.718639701730485</v>
+        <v>3.628350736522524</v>
       </c>
       <c r="D56">
-        <v>3.538039701730486</v>
+        <v>3.533850736522524</v>
       </c>
       <c r="E56">
-        <v>4.6494</v>
+        <v>4.7355</v>
       </c>
       <c r="F56">
-        <v>4.6494</v>
+        <v>4.7355</v>
       </c>
       <c r="G56">
         <v>4.83</v>
@@ -5879,28 +5879,28 @@
         <v>0.728</v>
       </c>
       <c r="M56">
-        <v>0.35242452</v>
+        <v>0.3589509</v>
       </c>
       <c r="N56">
-        <v>0.37557548</v>
+        <v>0.3690491</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>0.37557548</v>
+        <v>0.3690491</v>
       </c>
       <c r="Q56">
-        <v>0.8375754799999999</v>
+        <v>0.8310491</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1589757936678313</v>
+        <v>0.1614908113048942</v>
       </c>
       <c r="T56">
-        <v>2.072854406723368</v>
+        <v>2.118917837983887</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.065690548432896</v>
+        <v>2.028132538461388</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1143608650872024</v>
+        <v>0.1226128650872024</v>
       </c>
       <c r="C57">
-        <v>3.628350736522524</v>
+        <v>3.43079258352598</v>
       </c>
       <c r="D57">
-        <v>3.533850736522524</v>
+        <v>3.42239258352598</v>
       </c>
       <c r="E57">
-        <v>4.7355</v>
+        <v>4.8216</v>
       </c>
       <c r="F57">
-        <v>4.7355</v>
+        <v>4.8216</v>
       </c>
       <c r="G57">
         <v>4.83</v>
@@ -5961,45 +5961,45 @@
         <v>0.728</v>
       </c>
       <c r="M57">
-        <v>0.3589509</v>
+        <v>0.433944</v>
       </c>
       <c r="N57">
-        <v>0.3690491</v>
+        <v>0.294056</v>
       </c>
       <c r="O57">
         <v>0</v>
       </c>
       <c r="P57">
-        <v>0.3690491</v>
+        <v>0.294056</v>
       </c>
       <c r="Q57">
-        <v>0.8310491</v>
+        <v>0.7560560000000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1614908113048942</v>
+        <v>0.16412014792546</v>
       </c>
       <c r="T57">
-        <v>2.118917837983887</v>
+        <v>2.167075061574431</v>
       </c>
       <c r="U57">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V57">
         <v>0</v>
       </c>
       <c r="W57">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.028132538461388</v>
+        <v>1.677635823977287</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1226128650872024</v>
+        <v>0.1230548650872024</v>
       </c>
       <c r="C58">
-        <v>3.43079258352598</v>
+        <v>3.338920621727002</v>
       </c>
       <c r="D58">
-        <v>3.42239258352598</v>
+        <v>3.416620621727002</v>
       </c>
       <c r="E58">
-        <v>4.8216</v>
+        <v>4.9077</v>
       </c>
       <c r="F58">
-        <v>4.8216</v>
+        <v>4.9077</v>
       </c>
       <c r="G58">
         <v>4.83</v>
@@ -6043,28 +6043,28 @@
         <v>0.728</v>
       </c>
       <c r="M58">
-        <v>0.433944</v>
+        <v>0.441693</v>
       </c>
       <c r="N58">
-        <v>0.294056</v>
+        <v>0.286307</v>
       </c>
       <c r="O58">
         <v>0</v>
       </c>
       <c r="P58">
-        <v>0.294056</v>
+        <v>0.286307</v>
       </c>
       <c r="Q58">
-        <v>0.7560560000000001</v>
+        <v>0.7483070000000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.16412014792546</v>
+        <v>0.1668717792725637</v>
       </c>
       <c r="T58">
-        <v>2.167075061574431</v>
+        <v>2.21747215602965</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.677635823977287</v>
+        <v>1.648203616539089</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1230548650872024</v>
+        <v>0.1234968650872024</v>
       </c>
       <c r="C59">
-        <v>3.338920621727002</v>
+        <v>3.247068096301376</v>
       </c>
       <c r="D59">
-        <v>3.416620621727002</v>
+        <v>3.410868096301377</v>
       </c>
       <c r="E59">
-        <v>4.9077</v>
+        <v>4.9938</v>
       </c>
       <c r="F59">
-        <v>4.9077</v>
+        <v>4.9938</v>
       </c>
       <c r="G59">
         <v>4.83</v>
@@ -6125,28 +6125,28 @@
         <v>0.728</v>
       </c>
       <c r="M59">
-        <v>0.441693</v>
+        <v>0.449442</v>
       </c>
       <c r="N59">
-        <v>0.286307</v>
+        <v>0.278558</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>0.286307</v>
+        <v>0.278558</v>
       </c>
       <c r="Q59">
-        <v>0.7483070000000001</v>
+        <v>0.740558</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1668717792725637</v>
+        <v>0.1697544406838153</v>
       </c>
       <c r="T59">
-        <v>2.21747215602965</v>
+        <v>2.270269112125594</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.648203616539089</v>
+        <v>1.619786312805657</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1234968650872024</v>
+        <v>0.1239388650872024</v>
       </c>
       <c r="C60">
-        <v>3.247068096301377</v>
+        <v>3.155234909239719</v>
       </c>
       <c r="D60">
-        <v>3.410868096301377</v>
+        <v>3.405134909239718</v>
       </c>
       <c r="E60">
-        <v>4.993799999999999</v>
+        <v>5.079899999999999</v>
       </c>
       <c r="F60">
-        <v>4.993799999999999</v>
+        <v>5.079899999999999</v>
       </c>
       <c r="G60">
         <v>4.83</v>
@@ -6207,28 +6207,28 @@
         <v>0.728</v>
       </c>
       <c r="M60">
-        <v>0.449442</v>
+        <v>0.4571909999999999</v>
       </c>
       <c r="N60">
-        <v>0.278558</v>
+        <v>0.2708090000000001</v>
       </c>
       <c r="O60">
         <v>0</v>
       </c>
       <c r="P60">
-        <v>0.278558</v>
+        <v>0.2708090000000001</v>
       </c>
       <c r="Q60">
-        <v>0.740558</v>
+        <v>0.732809</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1697544406838152</v>
+        <v>0.1727777197248839</v>
       </c>
       <c r="T60">
-        <v>2.270269112125593</v>
+        <v>2.32564152949451</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.619786312805657</v>
+        <v>1.592332307503866</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1239388650872024</v>
+        <v>0.1243808650872024</v>
       </c>
       <c r="C61">
-        <v>3.155234909239719</v>
+        <v>3.063420963190489</v>
       </c>
       <c r="D61">
-        <v>3.405134909239718</v>
+        <v>3.399420963190489</v>
       </c>
       <c r="E61">
-        <v>5.079899999999999</v>
+        <v>5.165999999999999</v>
       </c>
       <c r="F61">
-        <v>5.079899999999999</v>
+        <v>5.165999999999999</v>
       </c>
       <c r="G61">
         <v>4.83</v>
@@ -6289,28 +6289,28 @@
         <v>0.728</v>
       </c>
       <c r="M61">
-        <v>0.4571909999999999</v>
+        <v>0.4649399999999999</v>
       </c>
       <c r="N61">
-        <v>0.2708090000000001</v>
+        <v>0.2630600000000001</v>
       </c>
       <c r="O61">
         <v>0</v>
       </c>
       <c r="P61">
-        <v>0.2708090000000001</v>
+        <v>0.2630600000000001</v>
       </c>
       <c r="Q61">
-        <v>0.732809</v>
+        <v>0.72506</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1727777197248839</v>
+        <v>0.175952162718006</v>
       </c>
       <c r="T61">
-        <v>2.32564152949451</v>
+        <v>2.383782567731873</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.592332307503866</v>
+        <v>1.565793435712135</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1243808650872024</v>
+        <v>0.1248228650872024</v>
       </c>
       <c r="C62">
-        <v>3.063420963190489</v>
+        <v>2.971626161454505</v>
       </c>
       <c r="D62">
-        <v>3.399420963190489</v>
+        <v>3.393726161454504</v>
       </c>
       <c r="E62">
-        <v>5.165999999999999</v>
+        <v>5.2521</v>
       </c>
       <c r="F62">
-        <v>5.165999999999999</v>
+        <v>5.2521</v>
       </c>
       <c r="G62">
         <v>4.83</v>
@@ -6371,28 +6371,28 @@
         <v>0.728</v>
       </c>
       <c r="M62">
-        <v>0.4649399999999999</v>
+        <v>0.4726889999999999</v>
       </c>
       <c r="N62">
-        <v>0.2630600000000001</v>
+        <v>0.2553110000000001</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>0.2630600000000001</v>
+        <v>0.2553110000000001</v>
       </c>
       <c r="Q62">
-        <v>0.72506</v>
+        <v>0.717311</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.175952162718006</v>
+        <v>0.1792893976594933</v>
       </c>
       <c r="T62">
-        <v>2.383782567731873</v>
+        <v>2.444905197673716</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.565793435712135</v>
+        <v>1.540124690864395</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1248228650872024</v>
+        <v>0.1252648650872024</v>
       </c>
       <c r="C63">
-        <v>2.971626161454505</v>
+        <v>2.879850407979458</v>
       </c>
       <c r="D63">
-        <v>3.393726161454504</v>
+        <v>3.388050407979458</v>
       </c>
       <c r="E63">
-        <v>5.2521</v>
+        <v>5.3382</v>
       </c>
       <c r="F63">
-        <v>5.2521</v>
+        <v>5.3382</v>
       </c>
       <c r="G63">
         <v>4.83</v>
@@ -6453,28 +6453,28 @@
         <v>0.728</v>
       </c>
       <c r="M63">
-        <v>0.4726889999999999</v>
+        <v>0.4804379999999999</v>
       </c>
       <c r="N63">
-        <v>0.2553110000000001</v>
+        <v>0.2475620000000001</v>
       </c>
       <c r="O63">
         <v>0</v>
       </c>
       <c r="P63">
-        <v>0.2553110000000001</v>
+        <v>0.2475620000000001</v>
       </c>
       <c r="Q63">
-        <v>0.717311</v>
+        <v>0.709562</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1792893976594933</v>
+        <v>0.1828022765452695</v>
       </c>
       <c r="T63">
-        <v>2.444905197673716</v>
+        <v>2.509244808138814</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.540124690864395</v>
+        <v>1.515283970044002</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1252648650872024</v>
+        <v>0.1614908650872024</v>
       </c>
       <c r="C64">
-        <v>2.879850407979458</v>
+        <v>2.385330211502507</v>
       </c>
       <c r="D64">
-        <v>3.388050407979458</v>
+        <v>2.979630211502507</v>
       </c>
       <c r="E64">
-        <v>5.3382</v>
+        <v>5.4243</v>
       </c>
       <c r="F64">
-        <v>5.3382</v>
+        <v>5.4243</v>
       </c>
       <c r="G64">
         <v>4.83</v>
@@ -6535,45 +6535,45 @@
         <v>0.728</v>
       </c>
       <c r="M64">
-        <v>0.4804379999999999</v>
+        <v>0.7962872400000001</v>
       </c>
       <c r="N64">
-        <v>0.2475620000000001</v>
+        <v>-0.06828724000000008</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P64">
-        <v>0.2475620000000001</v>
+        <v>-0.06828724000000008</v>
       </c>
       <c r="Q64">
-        <v>0.709562</v>
+        <v>0.3937127599999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1828022765452695</v>
+        <v>0.1865050407762227</v>
       </c>
       <c r="T64">
-        <v>2.509244808138814</v>
+        <v>2.577062235385809</v>
       </c>
       <c r="U64">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V64">
         <v>0</v>
       </c>
       <c r="W64">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>1.515283970044002</v>
+        <v>0.9142429558459331</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1614908650872024</v>
+        <v>0.1625008650872024</v>
       </c>
       <c r="C65">
-        <v>2.385330211502507</v>
+        <v>2.289249453523886</v>
       </c>
       <c r="D65">
-        <v>2.979630211502507</v>
+        <v>2.969649453523886</v>
       </c>
       <c r="E65">
-        <v>5.4243</v>
+        <v>5.5104</v>
       </c>
       <c r="F65">
-        <v>5.4243</v>
+        <v>5.5104</v>
       </c>
       <c r="G65">
         <v>4.83</v>
@@ -6617,28 +6617,28 @@
         <v>0.728</v>
       </c>
       <c r="M65">
-        <v>0.7962872400000001</v>
+        <v>0.80892672</v>
       </c>
       <c r="N65">
-        <v>-0.06828724000000008</v>
+        <v>-0.08092672000000001</v>
       </c>
       <c r="O65">
         <v>-0</v>
       </c>
       <c r="P65">
-        <v>-0.06828724000000008</v>
+        <v>-0.08092672000000001</v>
       </c>
       <c r="Q65">
-        <v>0.3937127599999999</v>
+        <v>0.38107328</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1865050407762227</v>
+        <v>0.1904135141311178</v>
       </c>
       <c r="T65">
-        <v>2.577062235385809</v>
+        <v>2.648647297479859</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.9142429558459331</v>
+        <v>0.8999579096608404</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1625008650872024</v>
+        <v>0.1635108650872024</v>
       </c>
       <c r="C66">
-        <v>2.289249453523886</v>
+        <v>2.193235336677403</v>
       </c>
       <c r="D66">
-        <v>2.969649453523886</v>
+        <v>2.959735336677403</v>
       </c>
       <c r="E66">
-        <v>5.5104</v>
+        <v>5.5965</v>
       </c>
       <c r="F66">
-        <v>5.5104</v>
+        <v>5.5965</v>
       </c>
       <c r="G66">
         <v>4.83</v>
@@ -6699,28 +6699,28 @@
         <v>0.728</v>
       </c>
       <c r="M66">
-        <v>0.80892672</v>
+        <v>0.8215662</v>
       </c>
       <c r="N66">
-        <v>-0.08092672000000001</v>
+        <v>-0.09356620000000004</v>
       </c>
       <c r="O66">
         <v>-0</v>
       </c>
       <c r="P66">
-        <v>-0.08092672000000001</v>
+        <v>-0.09356620000000004</v>
       </c>
       <c r="Q66">
-        <v>0.38107328</v>
+        <v>0.3684338</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1904135141311178</v>
+        <v>0.1945453288205783</v>
       </c>
       <c r="T66">
-        <v>2.648647297479859</v>
+        <v>2.724322934550713</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8999579096608404</v>
+        <v>0.8861124033583659</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1635108650872024</v>
+        <v>0.1645208650872024</v>
       </c>
       <c r="C67">
-        <v>2.193235336677403</v>
+        <v>2.097287195743516</v>
       </c>
       <c r="D67">
-        <v>2.959735336677403</v>
+        <v>2.949887195743516</v>
       </c>
       <c r="E67">
-        <v>5.5965</v>
+        <v>5.6826</v>
       </c>
       <c r="F67">
-        <v>5.5965</v>
+        <v>5.6826</v>
       </c>
       <c r="G67">
         <v>4.83</v>
@@ -6781,28 +6781,28 @@
         <v>0.728</v>
       </c>
       <c r="M67">
-        <v>0.8215662</v>
+        <v>0.8342056800000001</v>
       </c>
       <c r="N67">
-        <v>-0.09356620000000004</v>
+        <v>-0.1062056800000001</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>-0.09356620000000004</v>
+        <v>-0.1062056800000001</v>
       </c>
       <c r="Q67">
-        <v>0.3684338</v>
+        <v>0.3557943199999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1945453288205783</v>
+        <v>0.1989201914329483</v>
       </c>
       <c r="T67">
-        <v>2.724322934550713</v>
+        <v>2.804450079684557</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8861124033583659</v>
+        <v>0.8726864578529361</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1645208650872024</v>
+        <v>0.1655308650872024</v>
       </c>
       <c r="C68">
-        <v>2.097287195743516</v>
+        <v>2.001404374327052</v>
       </c>
       <c r="D68">
-        <v>2.949887195743516</v>
+        <v>2.940104374327052</v>
       </c>
       <c r="E68">
-        <v>5.6826</v>
+        <v>5.7687</v>
       </c>
       <c r="F68">
-        <v>5.6826</v>
+        <v>5.7687</v>
       </c>
       <c r="G68">
         <v>4.83</v>
@@ -6863,28 +6863,28 @@
         <v>0.728</v>
       </c>
       <c r="M68">
-        <v>0.8342056800000001</v>
+        <v>0.8468451600000001</v>
       </c>
       <c r="N68">
-        <v>-0.1062056800000001</v>
+        <v>-0.1188451600000001</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-0.1062056800000001</v>
+        <v>-0.1188451600000001</v>
       </c>
       <c r="Q68">
-        <v>0.3557943199999999</v>
+        <v>0.3431548399999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1989201914329483</v>
+        <v>0.2035601972339467</v>
       </c>
       <c r="T68">
-        <v>2.804450079684557</v>
+        <v>2.889433415432574</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8726864578529361</v>
+        <v>0.8596612868402057</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1655308650872024</v>
+        <v>0.1665408650872024</v>
       </c>
       <c r="C69">
-        <v>2.001404374327052</v>
+        <v>1.905586224711371</v>
       </c>
       <c r="D69">
-        <v>2.940104374327052</v>
+        <v>2.930386224711371</v>
       </c>
       <c r="E69">
-        <v>5.7687</v>
+        <v>5.8548</v>
       </c>
       <c r="F69">
-        <v>5.7687</v>
+        <v>5.8548</v>
       </c>
       <c r="G69">
         <v>4.83</v>
@@ -6945,28 +6945,28 @@
         <v>0.728</v>
       </c>
       <c r="M69">
-        <v>0.8468451600000001</v>
+        <v>0.8594846400000001</v>
       </c>
       <c r="N69">
-        <v>-0.1188451600000001</v>
+        <v>-0.1314846400000002</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-0.1188451600000001</v>
+        <v>-0.1314846400000002</v>
       </c>
       <c r="Q69">
-        <v>0.3431548399999999</v>
+        <v>0.3305153599999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2035601972339467</v>
+        <v>0.2084902033975075</v>
       </c>
       <c r="T69">
-        <v>2.889433415432574</v>
+        <v>2.979728209664842</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8596612868402057</v>
+        <v>0.8470192090925556</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1665408650872024</v>
+        <v>0.1675508650872024</v>
       </c>
       <c r="C70">
-        <v>1.905586224711371</v>
+        <v>1.809832107715406</v>
       </c>
       <c r="D70">
-        <v>2.930386224711371</v>
+        <v>2.920732107715406</v>
       </c>
       <c r="E70">
-        <v>5.8548</v>
+        <v>5.9409</v>
       </c>
       <c r="F70">
-        <v>5.8548</v>
+        <v>5.9409</v>
       </c>
       <c r="G70">
         <v>4.83</v>
@@ -7027,28 +7027,28 @@
         <v>0.728</v>
       </c>
       <c r="M70">
-        <v>0.8594846400000001</v>
+        <v>0.8721241200000001</v>
       </c>
       <c r="N70">
-        <v>-0.1314846400000002</v>
+        <v>-0.1441241200000001</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-0.1314846400000002</v>
+        <v>-0.1441241200000001</v>
       </c>
       <c r="Q70">
-        <v>0.3305153599999999</v>
+        <v>0.3178758799999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2084902033975075</v>
+        <v>0.2137382744748465</v>
       </c>
       <c r="T70">
-        <v>2.979728209664842</v>
+        <v>3.07584847449274</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8470192090925556</v>
+        <v>0.8347435683810693</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1675508650872024</v>
+        <v>0.1685608650872024</v>
       </c>
       <c r="C71">
-        <v>1.809832107715406</v>
+        <v>1.714141392553524</v>
       </c>
       <c r="D71">
-        <v>2.920732107715406</v>
+        <v>2.911141392553524</v>
       </c>
       <c r="E71">
-        <v>5.9409</v>
+        <v>6.027</v>
       </c>
       <c r="F71">
-        <v>5.9409</v>
+        <v>6.027</v>
       </c>
       <c r="G71">
         <v>4.83</v>
@@ -7109,28 +7109,28 @@
         <v>0.728</v>
       </c>
       <c r="M71">
-        <v>0.8721241200000001</v>
+        <v>0.8847636000000001</v>
       </c>
       <c r="N71">
-        <v>-0.1441241200000001</v>
+        <v>-0.1567636000000001</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-0.1441241200000001</v>
+        <v>-0.1567636000000001</v>
       </c>
       <c r="Q71">
-        <v>0.3178758799999999</v>
+        <v>0.3052363999999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2137382744748465</v>
+        <v>0.2193362169573414</v>
       </c>
       <c r="T71">
-        <v>3.07584847449274</v>
+        <v>3.178376756975831</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8347435683810693</v>
+        <v>0.8228186602613398</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1685608650872024</v>
+        <v>0.1695708650872024</v>
       </c>
       <c r="C72">
-        <v>1.714141392553524</v>
+        <v>1.61851345669814</v>
       </c>
       <c r="D72">
-        <v>2.911141392553524</v>
+        <v>2.90161345669814</v>
       </c>
       <c r="E72">
-        <v>6.027</v>
+        <v>6.1131</v>
       </c>
       <c r="F72">
-        <v>6.027</v>
+        <v>6.1131</v>
       </c>
       <c r="G72">
         <v>4.83</v>
@@ -7191,28 +7191,28 @@
         <v>0.728</v>
       </c>
       <c r="M72">
-        <v>0.8847636000000001</v>
+        <v>0.8974030800000001</v>
       </c>
       <c r="N72">
-        <v>-0.1567636000000001</v>
+        <v>-0.1694030800000002</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-0.1567636000000001</v>
+        <v>-0.1694030800000002</v>
       </c>
       <c r="Q72">
-        <v>0.3052363999999999</v>
+        <v>0.2925969199999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2193362169573414</v>
+        <v>0.2253202244386291</v>
       </c>
       <c r="T72">
-        <v>3.178376756975831</v>
+        <v>3.28797595549224</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8228186602613398</v>
+        <v>0.8112296650463913</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1695708650872024</v>
+        <v>0.2094608650872024</v>
       </c>
       <c r="C73">
-        <v>1.618513456698141</v>
+        <v>1.200272683174763</v>
       </c>
       <c r="D73">
-        <v>2.90161345669814</v>
+        <v>2.569472683174762</v>
       </c>
       <c r="E73">
-        <v>6.113099999999999</v>
+        <v>6.199199999999999</v>
       </c>
       <c r="F73">
-        <v>6.113099999999999</v>
+        <v>6.199199999999999</v>
       </c>
       <c r="G73">
         <v>4.83</v>
@@ -7273,45 +7273,45 @@
         <v>0.728</v>
       </c>
       <c r="M73">
-        <v>0.89740308</v>
+        <v>1.24479936</v>
       </c>
       <c r="N73">
-        <v>-0.16940308</v>
+        <v>-0.51679936</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-0.16940308</v>
+        <v>-0.51679936</v>
       </c>
       <c r="Q73">
-        <v>0.29259692</v>
+        <v>-0.05479936000000002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.225320224438629</v>
+        <v>0.2317316610257228</v>
       </c>
       <c r="T73">
-        <v>3.287975955492239</v>
+        <v>3.40540366818839</v>
       </c>
       <c r="U73">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
         <v>0</v>
       </c>
       <c r="W73">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.8112296650463914</v>
+        <v>0.5848332055697715</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2094608650872024</v>
+        <v>0.2110108650872024</v>
       </c>
       <c r="C74">
-        <v>1.200272683174763</v>
+        <v>1.102794657520906</v>
       </c>
       <c r="D74">
-        <v>2.569472683174762</v>
+        <v>2.558094657520905</v>
       </c>
       <c r="E74">
-        <v>6.199199999999999</v>
+        <v>6.285299999999999</v>
       </c>
       <c r="F74">
-        <v>6.199199999999999</v>
+        <v>6.285299999999999</v>
       </c>
       <c r="G74">
         <v>4.83</v>
@@ -7355,28 +7355,28 @@
         <v>0.728</v>
       </c>
       <c r="M74">
-        <v>1.24479936</v>
+        <v>1.26208824</v>
       </c>
       <c r="N74">
-        <v>-0.51679936</v>
+        <v>-0.53408824</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-0.51679936</v>
+        <v>-0.53408824</v>
       </c>
       <c r="Q74">
-        <v>-0.05479936000000002</v>
+        <v>-0.07208823999999997</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2317316610257228</v>
+        <v>0.2386180188414904</v>
       </c>
       <c r="T74">
-        <v>3.40540366818839</v>
+        <v>3.531529729973145</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5848332055697715</v>
+        <v>0.5768217917948431</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2110108650872024</v>
+        <v>0.2125608650872024</v>
       </c>
       <c r="C75">
-        <v>1.102794657520906</v>
+        <v>1.005416954963876</v>
       </c>
       <c r="D75">
-        <v>2.558094657520905</v>
+        <v>2.546816954963876</v>
       </c>
       <c r="E75">
-        <v>6.285299999999999</v>
+        <v>6.3714</v>
       </c>
       <c r="F75">
-        <v>6.285299999999999</v>
+        <v>6.3714</v>
       </c>
       <c r="G75">
         <v>4.83</v>
@@ -7437,28 +7437,28 @@
         <v>0.728</v>
       </c>
       <c r="M75">
-        <v>1.26208824</v>
+        <v>1.27937712</v>
       </c>
       <c r="N75">
-        <v>-0.53408824</v>
+        <v>-0.5513771199999999</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-0.53408824</v>
+        <v>-0.5513771199999999</v>
       </c>
       <c r="Q75">
-        <v>-0.07208823999999997</v>
+        <v>-0.08937711999999992</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2386180188414904</v>
+        <v>0.24603409648924</v>
       </c>
       <c r="T75">
-        <v>3.531529729973145</v>
+        <v>3.667357796510574</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5768217917948431</v>
+        <v>0.5690269027165344</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2125608650872024</v>
+        <v>0.2141108650872024</v>
       </c>
       <c r="C76">
-        <v>1.005416954963876</v>
+        <v>0.9081382544642684</v>
       </c>
       <c r="D76">
-        <v>2.546816954963876</v>
+        <v>2.535638254464268</v>
       </c>
       <c r="E76">
-        <v>6.3714</v>
+        <v>6.4575</v>
       </c>
       <c r="F76">
-        <v>6.3714</v>
+        <v>6.4575</v>
       </c>
       <c r="G76">
         <v>4.83</v>
@@ -7519,28 +7519,28 @@
         <v>0.728</v>
       </c>
       <c r="M76">
-        <v>1.27937712</v>
+        <v>1.296666</v>
       </c>
       <c r="N76">
-        <v>-0.5513771199999999</v>
+        <v>-0.5686659999999999</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-0.5513771199999999</v>
+        <v>-0.5686659999999999</v>
       </c>
       <c r="Q76">
-        <v>-0.08937711999999992</v>
+        <v>-0.1066659999999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.24603409648924</v>
+        <v>0.2540434603488096</v>
       </c>
       <c r="T76">
-        <v>3.667357796510574</v>
+        <v>3.814052108370997</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5690269027165344</v>
+        <v>0.5614398773469806</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2141108650872024</v>
+        <v>0.2156608650872024</v>
       </c>
       <c r="C77">
-        <v>0.9081382544642684</v>
+        <v>0.8109572580749802</v>
       </c>
       <c r="D77">
-        <v>2.535638254464268</v>
+        <v>2.52455725807498</v>
       </c>
       <c r="E77">
-        <v>6.4575</v>
+        <v>6.5436</v>
       </c>
       <c r="F77">
-        <v>6.4575</v>
+        <v>6.5436</v>
       </c>
       <c r="G77">
         <v>4.83</v>
@@ -7601,28 +7601,28 @@
         <v>0.728</v>
       </c>
       <c r="M77">
-        <v>1.296666</v>
+        <v>1.31395488</v>
       </c>
       <c r="N77">
-        <v>-0.5686659999999999</v>
+        <v>-0.5859548800000001</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-0.5686659999999999</v>
+        <v>-0.5859548800000001</v>
       </c>
       <c r="Q77">
-        <v>-0.1066659999999999</v>
+        <v>-0.12395488</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2540434603488096</v>
+        <v>0.2627202711966767</v>
       </c>
       <c r="T77">
-        <v>3.814052108370997</v>
+        <v>3.972970946219789</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5614398773469806</v>
+        <v>0.5540525105397835</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2156608650872024</v>
+        <v>0.2172108650872024</v>
       </c>
       <c r="C78">
-        <v>0.8109572580749802</v>
+        <v>0.7138726904388335</v>
       </c>
       <c r="D78">
-        <v>2.52455725807498</v>
+        <v>2.513572690438833</v>
       </c>
       <c r="E78">
-        <v>6.5436</v>
+        <v>6.6297</v>
       </c>
       <c r="F78">
-        <v>6.5436</v>
+        <v>6.6297</v>
       </c>
       <c r="G78">
         <v>4.83</v>
@@ -7683,28 +7683,28 @@
         <v>0.728</v>
       </c>
       <c r="M78">
-        <v>1.31395488</v>
+        <v>1.33124376</v>
       </c>
       <c r="N78">
-        <v>-0.5859548800000001</v>
+        <v>-0.60324376</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-0.5859548800000001</v>
+        <v>-0.60324376</v>
       </c>
       <c r="Q78">
-        <v>-0.12395488</v>
+        <v>-0.14124376</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2627202711966767</v>
+        <v>0.2721515873356626</v>
       </c>
       <c r="T78">
-        <v>3.972970946219789</v>
+        <v>4.145708813446736</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5540525105397835</v>
+        <v>0.5468570233899162</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2172108650872024</v>
+        <v>0.2187608650872024</v>
       </c>
       <c r="C79">
-        <v>0.7138726904388335</v>
+        <v>0.6168832982992445</v>
       </c>
       <c r="D79">
-        <v>2.513572690438833</v>
+        <v>2.502683298299244</v>
       </c>
       <c r="E79">
-        <v>6.6297</v>
+        <v>6.7158</v>
       </c>
       <c r="F79">
-        <v>6.6297</v>
+        <v>6.7158</v>
       </c>
       <c r="G79">
         <v>4.83</v>
@@ -7765,28 +7765,28 @@
         <v>0.728</v>
       </c>
       <c r="M79">
-        <v>1.33124376</v>
+        <v>1.34853264</v>
       </c>
       <c r="N79">
-        <v>-0.60324376</v>
+        <v>-0.62053264</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-0.60324376</v>
+        <v>-0.62053264</v>
       </c>
       <c r="Q79">
-        <v>-0.14124376</v>
+        <v>-0.1585326399999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2721515873356626</v>
+        <v>0.28244029585092</v>
       </c>
       <c r="T79">
-        <v>4.145708813446736</v>
+        <v>4.334150123148861</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5468570233899162</v>
+        <v>0.5398460359105584</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2187608650872024</v>
+        <v>0.2203108650872024</v>
       </c>
       <c r="C80">
-        <v>0.6168832982992445</v>
+        <v>0.5199878500235684</v>
       </c>
       <c r="D80">
-        <v>2.502683298299244</v>
+        <v>2.491887850023568</v>
       </c>
       <c r="E80">
-        <v>6.7158</v>
+        <v>6.8019</v>
       </c>
       <c r="F80">
-        <v>6.7158</v>
+        <v>6.8019</v>
       </c>
       <c r="G80">
         <v>4.83</v>
@@ -7847,28 +7847,28 @@
         <v>0.728</v>
       </c>
       <c r="M80">
-        <v>1.34853264</v>
+        <v>1.36582152</v>
       </c>
       <c r="N80">
-        <v>-0.62053264</v>
+        <v>-0.6378215199999999</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-0.62053264</v>
+        <v>-0.6378215199999999</v>
       </c>
       <c r="Q80">
-        <v>-0.1585326399999999</v>
+        <v>-0.1758215199999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.28244029585092</v>
+        <v>0.2937088813676305</v>
       </c>
       <c r="T80">
-        <v>4.334150123148861</v>
+        <v>4.540538224251188</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5398460359105584</v>
+        <v>0.5330125417851082</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2203108650872024</v>
+        <v>0.2218608650872024</v>
       </c>
       <c r="C81">
-        <v>0.5199878500235684</v>
+        <v>0.4231851351387217</v>
       </c>
       <c r="D81">
-        <v>2.491887850023568</v>
+        <v>2.481185135138721</v>
       </c>
       <c r="E81">
-        <v>6.8019</v>
+        <v>6.888</v>
       </c>
       <c r="F81">
-        <v>6.8019</v>
+        <v>6.888</v>
       </c>
       <c r="G81">
         <v>4.83</v>
@@ -7929,28 +7929,28 @@
         <v>0.728</v>
       </c>
       <c r="M81">
-        <v>1.36582152</v>
+        <v>1.3831104</v>
       </c>
       <c r="N81">
-        <v>-0.6378215199999999</v>
+        <v>-0.6551104000000001</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-0.6378215199999999</v>
+        <v>-0.6551104000000001</v>
       </c>
       <c r="Q81">
-        <v>-0.1758215199999999</v>
+        <v>-0.1931104000000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2937088813676305</v>
+        <v>0.3061043254360121</v>
       </c>
       <c r="T81">
-        <v>4.540538224251188</v>
+        <v>4.767565135463747</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5330125417851082</v>
+        <v>0.5263498850127943</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2218608650872024</v>
+        <v>0.2234108650872024</v>
       </c>
       <c r="C82">
-        <v>0.4231851351387217</v>
+        <v>0.3264739638787173</v>
       </c>
       <c r="D82">
-        <v>2.481185135138721</v>
+        <v>2.470573963878717</v>
       </c>
       <c r="E82">
-        <v>6.888</v>
+        <v>6.9741</v>
       </c>
       <c r="F82">
-        <v>6.888</v>
+        <v>6.9741</v>
       </c>
       <c r="G82">
         <v>4.83</v>
@@ -8011,28 +8011,28 @@
         <v>0.728</v>
       </c>
       <c r="M82">
-        <v>1.3831104</v>
+        <v>1.40039928</v>
       </c>
       <c r="N82">
-        <v>-0.6551104000000001</v>
+        <v>-0.67239928</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-0.6551104000000001</v>
+        <v>-0.67239928</v>
       </c>
       <c r="Q82">
-        <v>-0.1931104000000001</v>
+        <v>-0.21039928</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3061043254360121</v>
+        <v>0.3198045530905391</v>
       </c>
       <c r="T82">
-        <v>4.767565135463747</v>
+        <v>5.01848961627763</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5263498850127943</v>
+        <v>0.5198517382842414</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2234108650872024</v>
+        <v>0.2249608650872024</v>
       </c>
       <c r="C83">
-        <v>0.3264739638787173</v>
+        <v>0.2298531667437747</v>
       </c>
       <c r="D83">
-        <v>2.470573963878717</v>
+        <v>2.460053166743774</v>
       </c>
       <c r="E83">
-        <v>6.9741</v>
+        <v>7.0602</v>
       </c>
       <c r="F83">
-        <v>6.9741</v>
+        <v>7.0602</v>
       </c>
       <c r="G83">
         <v>4.83</v>
@@ -8093,28 +8093,28 @@
         <v>0.728</v>
       </c>
       <c r="M83">
-        <v>1.40039928</v>
+        <v>1.41768816</v>
       </c>
       <c r="N83">
-        <v>-0.67239928</v>
+        <v>-0.68968816</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-0.67239928</v>
+        <v>-0.68968816</v>
       </c>
       <c r="Q83">
-        <v>-0.21039928</v>
+        <v>-0.22768816</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3198045530905391</v>
+        <v>0.3350270282622356</v>
       </c>
       <c r="T83">
-        <v>5.01848961627763</v>
+        <v>5.29729459495972</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5198517382842414</v>
+        <v>0.5135120829393116</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2249608650872024</v>
+        <v>0.2265108650872024</v>
       </c>
       <c r="C84">
-        <v>0.2298531667437747</v>
+        <v>0.1333215940706243</v>
       </c>
       <c r="D84">
-        <v>2.460053166743774</v>
+        <v>2.449621594070624</v>
       </c>
       <c r="E84">
-        <v>7.0602</v>
+        <v>7.1463</v>
       </c>
       <c r="F84">
-        <v>7.0602</v>
+        <v>7.1463</v>
       </c>
       <c r="G84">
         <v>4.83</v>
@@ -8175,28 +8175,28 @@
         <v>0.728</v>
       </c>
       <c r="M84">
-        <v>1.41768816</v>
+        <v>1.43497704</v>
       </c>
       <c r="N84">
-        <v>-0.68968816</v>
+        <v>-0.7069770400000002</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-0.68968816</v>
+        <v>-0.7069770400000002</v>
       </c>
       <c r="Q84">
-        <v>-0.22768816</v>
+        <v>-0.2449770400000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3350270282622356</v>
+        <v>0.3520403828658966</v>
       </c>
       <c r="T84">
-        <v>5.29729459495972</v>
+        <v>5.608900159369115</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5135120829393116</v>
+        <v>0.5073251903737777</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2265108650872024</v>
+        <v>0.2280608650872024</v>
       </c>
       <c r="C85">
-        <v>0.1333215940706243</v>
+        <v>0.0368781156137219</v>
       </c>
       <c r="D85">
-        <v>2.449621594070624</v>
+        <v>2.439278115613722</v>
       </c>
       <c r="E85">
-        <v>7.1463</v>
+        <v>7.2324</v>
       </c>
       <c r="F85">
-        <v>7.1463</v>
+        <v>7.2324</v>
       </c>
       <c r="G85">
         <v>4.83</v>
@@ -8257,28 +8257,28 @@
         <v>0.728</v>
       </c>
       <c r="M85">
-        <v>1.43497704</v>
+        <v>1.45226592</v>
       </c>
       <c r="N85">
-        <v>-0.7069770400000002</v>
+        <v>-0.7242659200000001</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-0.7069770400000002</v>
+        <v>-0.7242659200000001</v>
       </c>
       <c r="Q85">
-        <v>-0.2449770400000001</v>
+        <v>-0.2622659200000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3520403828658966</v>
+        <v>0.3711804067950152</v>
       </c>
       <c r="T85">
-        <v>5.608900159369115</v>
+        <v>5.959456419329687</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5073251903737777</v>
+        <v>0.5012856047740898</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2280608650872024</v>
+        <v>0.2593608650872024</v>
       </c>
       <c r="C86">
-        <v>0.03687811561372278</v>
+        <v>-0.2408702108696277</v>
       </c>
       <c r="D86">
-        <v>2.439278115613722</v>
+        <v>2.247629789130372</v>
       </c>
       <c r="E86">
-        <v>7.232399999999999</v>
+        <v>7.318499999999999</v>
       </c>
       <c r="F86">
-        <v>7.232399999999999</v>
+        <v>7.318499999999999</v>
       </c>
       <c r="G86">
         <v>4.83</v>
@@ -8339,45 +8339,45 @@
         <v>0.728</v>
       </c>
       <c r="M86">
-        <v>1.45226592</v>
+        <v>1.7257023</v>
       </c>
       <c r="N86">
-        <v>-0.7242659199999999</v>
+        <v>-0.9977023</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-0.7242659199999999</v>
+        <v>-0.9977023</v>
       </c>
       <c r="Q86">
-        <v>-0.2622659199999999</v>
+        <v>-0.5357023000000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.371180406795015</v>
+        <v>0.3928724339146827</v>
       </c>
       <c r="T86">
-        <v>5.959456419329682</v>
+        <v>6.356753513951662</v>
       </c>
       <c r="U86">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
         <v>0</v>
       </c>
       <c r="W86">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.5012856047740899</v>
+        <v>0.4218572345879124</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2593608650872024</v>
+        <v>0.2612608650872024</v>
       </c>
       <c r="C87">
-        <v>-0.2408702108696277</v>
+        <v>-0.337638908471658</v>
       </c>
       <c r="D87">
-        <v>2.247629789130372</v>
+        <v>2.236961091528341</v>
       </c>
       <c r="E87">
-        <v>7.318499999999999</v>
+        <v>7.404599999999999</v>
       </c>
       <c r="F87">
-        <v>7.318499999999999</v>
+        <v>7.404599999999999</v>
       </c>
       <c r="G87">
         <v>4.83</v>
@@ -8421,28 +8421,28 @@
         <v>0.728</v>
       </c>
       <c r="M87">
-        <v>1.7257023</v>
+        <v>1.74600468</v>
       </c>
       <c r="N87">
-        <v>-0.9977023</v>
+        <v>-1.01800468</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-0.9977023</v>
+        <v>-1.01800468</v>
       </c>
       <c r="Q87">
-        <v>-0.5357023000000001</v>
+        <v>-0.55600468</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3928724339146827</v>
+        <v>0.4176633220514457</v>
       </c>
       <c r="T87">
-        <v>6.356753513951662</v>
+        <v>6.81080733637678</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4218572345879124</v>
+        <v>0.4169519179066576</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2612608650872024</v>
+        <v>0.2631608650872024</v>
       </c>
       <c r="C88">
-        <v>-0.337638908471658</v>
+        <v>-0.4343068035365638</v>
       </c>
       <c r="D88">
-        <v>2.236961091528341</v>
+        <v>2.226393196463436</v>
       </c>
       <c r="E88">
-        <v>7.404599999999999</v>
+        <v>7.490699999999999</v>
       </c>
       <c r="F88">
-        <v>7.404599999999999</v>
+        <v>7.490699999999999</v>
       </c>
       <c r="G88">
         <v>4.83</v>
@@ -8503,28 +8503,28 @@
         <v>0.728</v>
       </c>
       <c r="M88">
-        <v>1.74600468</v>
+        <v>1.76630706</v>
       </c>
       <c r="N88">
-        <v>-1.01800468</v>
+        <v>-1.03830706</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-1.01800468</v>
+        <v>-1.03830706</v>
       </c>
       <c r="Q88">
-        <v>-0.55600468</v>
+        <v>-0.57630706</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4176633220514457</v>
+        <v>0.44626819297848</v>
       </c>
       <c r="T88">
-        <v>6.81080733637678</v>
+        <v>7.334715593021148</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4169519179066576</v>
+        <v>0.4121593671261213</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2631608650872024</v>
+        <v>0.2650608650872024</v>
       </c>
       <c r="C89">
-        <v>-0.4343068035365638</v>
+        <v>-0.5308753179867871</v>
       </c>
       <c r="D89">
-        <v>2.226393196463436</v>
+        <v>2.215924682013212</v>
       </c>
       <c r="E89">
-        <v>7.490699999999999</v>
+        <v>7.5768</v>
       </c>
       <c r="F89">
-        <v>7.490699999999999</v>
+        <v>7.5768</v>
       </c>
       <c r="G89">
         <v>4.83</v>
@@ -8585,28 +8585,28 @@
         <v>0.728</v>
       </c>
       <c r="M89">
-        <v>1.76630706</v>
+        <v>1.78660944</v>
       </c>
       <c r="N89">
-        <v>-1.03830706</v>
+        <v>-1.05860944</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-1.03830706</v>
+        <v>-1.05860944</v>
       </c>
       <c r="Q89">
-        <v>-0.57630706</v>
+        <v>-0.5966094399999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.44626819297848</v>
+        <v>0.4796405423933534</v>
       </c>
       <c r="T89">
-        <v>7.334715593021148</v>
+        <v>7.945941892439579</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4121593671261213</v>
+        <v>0.4074757379542336</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2650608650872024</v>
+        <v>0.2669608650872024</v>
       </c>
       <c r="C90">
-        <v>-0.5308753179867871</v>
+        <v>-0.6273458471263762</v>
       </c>
       <c r="D90">
-        <v>2.215924682013212</v>
+        <v>2.205554152873623</v>
       </c>
       <c r="E90">
-        <v>7.5768</v>
+        <v>7.6629</v>
       </c>
       <c r="F90">
-        <v>7.5768</v>
+        <v>7.6629</v>
       </c>
       <c r="G90">
         <v>4.83</v>
@@ -8667,28 +8667,28 @@
         <v>0.728</v>
       </c>
       <c r="M90">
-        <v>1.78660944</v>
+        <v>1.80691182</v>
       </c>
       <c r="N90">
-        <v>-1.05860944</v>
+        <v>-1.07891182</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-1.05860944</v>
+        <v>-1.07891182</v>
       </c>
       <c r="Q90">
-        <v>-0.5966094399999999</v>
+        <v>-0.6169118200000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4796405423933534</v>
+        <v>0.5190805917018401</v>
       </c>
       <c r="T90">
-        <v>7.945941892439579</v>
+        <v>8.668300246297722</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4074757379542336</v>
+        <v>0.4028973588760961</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2669608650872024</v>
+        <v>0.2688608650872024</v>
       </c>
       <c r="C91">
-        <v>-0.6273458471263762</v>
+        <v>-0.7237197602609573</v>
       </c>
       <c r="D91">
-        <v>2.205554152873623</v>
+        <v>2.195280239739042</v>
       </c>
       <c r="E91">
-        <v>7.6629</v>
+        <v>7.749</v>
       </c>
       <c r="F91">
-        <v>7.6629</v>
+        <v>7.749</v>
       </c>
       <c r="G91">
         <v>4.83</v>
@@ -8749,28 +8749,28 @@
         <v>0.728</v>
       </c>
       <c r="M91">
-        <v>1.80691182</v>
+        <v>1.8272142</v>
       </c>
       <c r="N91">
-        <v>-1.07891182</v>
+        <v>-1.0992142</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-1.07891182</v>
+        <v>-1.0992142</v>
       </c>
       <c r="Q91">
-        <v>-0.6169118200000001</v>
+        <v>-0.6372142000000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5190805917018401</v>
+        <v>0.5664086508720241</v>
       </c>
       <c r="T91">
-        <v>8.668300246297722</v>
+        <v>9.535130270927494</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4028973588760961</v>
+        <v>0.3984207215552505</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2688608650872024</v>
+        <v>0.2707608650872024</v>
       </c>
       <c r="C92">
-        <v>-0.7237197602609573</v>
+        <v>-0.8199984013004551</v>
       </c>
       <c r="D92">
-        <v>2.195280239739042</v>
+        <v>2.185101598699545</v>
       </c>
       <c r="E92">
-        <v>7.749</v>
+        <v>7.8351</v>
       </c>
       <c r="F92">
-        <v>7.749</v>
+        <v>7.8351</v>
       </c>
       <c r="G92">
         <v>4.83</v>
@@ -8831,28 +8831,28 @@
         <v>0.728</v>
       </c>
       <c r="M92">
-        <v>1.8272142</v>
+        <v>1.84751658</v>
       </c>
       <c r="N92">
-        <v>-1.0992142</v>
+        <v>-1.11951658</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-1.0992142</v>
+        <v>-1.11951658</v>
       </c>
       <c r="Q92">
-        <v>-0.6372142000000001</v>
+        <v>-0.65751658</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5664086508720241</v>
+        <v>0.6242540565244712</v>
       </c>
       <c r="T92">
-        <v>9.535130270927494</v>
+        <v>10.59458918991944</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3984207215552505</v>
+        <v>0.3940424718678303</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2707608650872024</v>
+        <v>0.2726608650872024</v>
       </c>
       <c r="C93">
-        <v>-0.8199984013004551</v>
+        <v>-0.9161830893451226</v>
       </c>
       <c r="D93">
-        <v>2.185101598699545</v>
+        <v>2.175016910654877</v>
       </c>
       <c r="E93">
-        <v>7.8351</v>
+        <v>7.9212</v>
       </c>
       <c r="F93">
-        <v>7.8351</v>
+        <v>7.9212</v>
       </c>
       <c r="G93">
         <v>4.83</v>
@@ -8913,28 +8913,28 @@
         <v>0.728</v>
       </c>
       <c r="M93">
-        <v>1.84751658</v>
+        <v>1.86781896</v>
       </c>
       <c r="N93">
-        <v>-1.11951658</v>
+        <v>-1.13981896</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-1.11951658</v>
+        <v>-1.13981896</v>
       </c>
       <c r="Q93">
-        <v>-0.65751658</v>
+        <v>-0.67781896</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6242540565244712</v>
+        <v>0.6965608135900304</v>
       </c>
       <c r="T93">
-        <v>10.59458918991944</v>
+        <v>11.91891283865937</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3940424718678303</v>
+        <v>0.3897594015214408</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2726608650872024</v>
+        <v>0.2745608650872024</v>
       </c>
       <c r="C94">
-        <v>-0.9161830893451226</v>
+        <v>-1.012275119255426</v>
       </c>
       <c r="D94">
-        <v>2.175016910654877</v>
+        <v>2.165024880744575</v>
       </c>
       <c r="E94">
-        <v>7.9212</v>
+        <v>8.007300000000001</v>
       </c>
       <c r="F94">
-        <v>7.9212</v>
+        <v>8.007300000000001</v>
       </c>
       <c r="G94">
         <v>4.83</v>
@@ -8995,28 +8995,28 @@
         <v>0.728</v>
       </c>
       <c r="M94">
-        <v>1.86781896</v>
+        <v>1.88812134</v>
       </c>
       <c r="N94">
-        <v>-1.13981896</v>
+        <v>-1.16012134</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-1.13981896</v>
+        <v>-1.16012134</v>
       </c>
       <c r="Q94">
-        <v>-0.67781896</v>
+        <v>-0.6981213400000004</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6965608135900304</v>
+        <v>0.789526644102892</v>
       </c>
       <c r="T94">
-        <v>11.91891283865937</v>
+        <v>13.62161467275357</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3897594015214408</v>
+        <v>0.3855684402147586</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2745608650872024</v>
+        <v>0.2764608650872024</v>
       </c>
       <c r="C95">
-        <v>-1.012275119255426</v>
+        <v>-1.108275762206274</v>
       </c>
       <c r="D95">
-        <v>2.165024880744575</v>
+        <v>2.155124237793727</v>
       </c>
       <c r="E95">
-        <v>8.007300000000001</v>
+        <v>8.093400000000001</v>
       </c>
       <c r="F95">
-        <v>8.007300000000001</v>
+        <v>8.093400000000001</v>
       </c>
       <c r="G95">
         <v>4.83</v>
@@ -9077,28 +9077,28 @@
         <v>0.728</v>
       </c>
       <c r="M95">
-        <v>1.88812134</v>
+        <v>1.90842372</v>
       </c>
       <c r="N95">
-        <v>-1.16012134</v>
+        <v>-1.18042372</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-1.16012134</v>
+        <v>-1.18042372</v>
       </c>
       <c r="Q95">
-        <v>-0.6981213400000004</v>
+        <v>-0.7184237200000003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.789526644102892</v>
+        <v>0.9134810847867074</v>
       </c>
       <c r="T95">
-        <v>13.62161467275357</v>
+        <v>15.89188378487917</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3855684402147586</v>
+        <v>0.3814666482975803</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2764608650872024</v>
+        <v>0.2783608650872024</v>
       </c>
       <c r="C96">
-        <v>-1.108275762206274</v>
+        <v>-1.204186266226136</v>
       </c>
       <c r="D96">
-        <v>2.155124237793727</v>
+        <v>2.145313733773865</v>
       </c>
       <c r="E96">
-        <v>8.093400000000001</v>
+        <v>8.179500000000001</v>
       </c>
       <c r="F96">
-        <v>8.093400000000001</v>
+        <v>8.179500000000001</v>
       </c>
       <c r="G96">
         <v>4.83</v>
@@ -9159,28 +9159,28 @@
         <v>0.728</v>
       </c>
       <c r="M96">
-        <v>1.90842372</v>
+        <v>1.9287261</v>
       </c>
       <c r="N96">
-        <v>-1.18042372</v>
+        <v>-1.2007261</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-1.18042372</v>
+        <v>-1.2007261</v>
       </c>
       <c r="Q96">
-        <v>-0.7184237200000003</v>
+        <v>-0.7387261000000003</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9134810847867074</v>
+        <v>1.08701730174405</v>
       </c>
       <c r="T96">
-        <v>15.89188378487917</v>
+        <v>19.07026054185501</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3814666482975803</v>
+        <v>0.3774512098944479</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2783608650872024</v>
+        <v>0.2802608650872024</v>
       </c>
       <c r="C97">
-        <v>-1.204186266226136</v>
+        <v>-1.300007856721479</v>
       </c>
       <c r="D97">
-        <v>2.145313733773865</v>
+        <v>2.135592143278521</v>
       </c>
       <c r="E97">
-        <v>8.179500000000001</v>
+        <v>8.265600000000001</v>
       </c>
       <c r="F97">
-        <v>8.179500000000001</v>
+        <v>8.265600000000001</v>
       </c>
       <c r="G97">
         <v>4.83</v>
@@ -9241,28 +9241,28 @@
         <v>0.728</v>
       </c>
       <c r="M97">
-        <v>1.9287261</v>
+        <v>1.94902848</v>
       </c>
       <c r="N97">
-        <v>-1.2007261</v>
+        <v>-1.22102848</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-1.2007261</v>
+        <v>-1.22102848</v>
       </c>
       <c r="Q97">
-        <v>-0.7387261000000003</v>
+        <v>-0.7590284800000004</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.08701730174405</v>
+        <v>1.347321627180063</v>
       </c>
       <c r="T97">
-        <v>19.07026054185501</v>
+        <v>23.83782567731878</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3774512098944479</v>
+        <v>0.3735194264580474</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2802608650872024</v>
+        <v>0.2821608650872024</v>
       </c>
       <c r="C98">
-        <v>-1.300007856721478</v>
+        <v>-1.395741736987022</v>
       </c>
       <c r="D98">
-        <v>2.135592143278521</v>
+        <v>2.125958263012978</v>
       </c>
       <c r="E98">
-        <v>8.265599999999999</v>
+        <v>8.351699999999999</v>
       </c>
       <c r="F98">
-        <v>8.265599999999999</v>
+        <v>8.351699999999999</v>
       </c>
       <c r="G98">
         <v>4.83</v>
@@ -9323,28 +9323,28 @@
         <v>0.728</v>
       </c>
       <c r="M98">
-        <v>1.94902848</v>
+        <v>1.96933086</v>
       </c>
       <c r="N98">
-        <v>-1.22102848</v>
+        <v>-1.24133086</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-1.22102848</v>
+        <v>-1.24133086</v>
       </c>
       <c r="Q98">
-        <v>-0.75902848</v>
+        <v>-0.77933086</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.347321627180059</v>
+        <v>1.781162169573412</v>
       </c>
       <c r="T98">
-        <v>23.83782567731871</v>
+        <v>31.78376756975829</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3735194264580475</v>
+        <v>0.3696687107213665</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2821608650872024</v>
+        <v>0.2840608650872024</v>
       </c>
       <c r="C99">
-        <v>-1.395741736987022</v>
+        <v>-1.491389088702237</v>
       </c>
       <c r="D99">
-        <v>2.125958263012978</v>
+        <v>2.116410911297762</v>
       </c>
       <c r="E99">
-        <v>8.351699999999999</v>
+        <v>8.437799999999999</v>
       </c>
       <c r="F99">
-        <v>8.351699999999999</v>
+        <v>8.437799999999999</v>
       </c>
       <c r="G99">
         <v>4.83</v>
@@ -9405,28 +9405,28 @@
         <v>0.728</v>
       </c>
       <c r="M99">
-        <v>1.96933086</v>
+        <v>1.98963324</v>
       </c>
       <c r="N99">
-        <v>-1.24133086</v>
+        <v>-1.26163324</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-1.24133086</v>
+        <v>-1.26163324</v>
       </c>
       <c r="Q99">
-        <v>-0.77933086</v>
+        <v>-0.7996332399999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.781162169573412</v>
+        <v>2.648843254360118</v>
       </c>
       <c r="T99">
-        <v>31.78376756975829</v>
+        <v>47.67565135463742</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3696687107213665</v>
+        <v>0.3658965810201281</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2840608650872024</v>
+        <v>0.2859608650872024</v>
       </c>
       <c r="C100">
-        <v>-1.491389088702237</v>
+        <v>-1.586951072414537</v>
       </c>
       <c r="D100">
-        <v>2.116410911297762</v>
+        <v>2.106948927585463</v>
       </c>
       <c r="E100">
-        <v>8.437799999999999</v>
+        <v>8.523899999999999</v>
       </c>
       <c r="F100">
-        <v>8.437799999999999</v>
+        <v>8.523899999999999</v>
       </c>
       <c r="G100">
         <v>4.83</v>
@@ -9487,28 +9487,28 @@
         <v>0.728</v>
       </c>
       <c r="M100">
-        <v>1.98963324</v>
+        <v>2.00993562</v>
       </c>
       <c r="N100">
-        <v>-1.26163324</v>
+        <v>-1.28193562</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-1.26163324</v>
+        <v>-1.28193562</v>
       </c>
       <c r="Q100">
-        <v>-0.7996332399999999</v>
+        <v>-0.8199356199999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.648843254360118</v>
+        <v>5.251886508720236</v>
       </c>
       <c r="T100">
-        <v>47.67565135463742</v>
+        <v>95.35130270927485</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3658965810201281</v>
+        <v>0.3622006559593187</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2859608650872024</v>
-      </c>
-      <c r="C101">
-        <v>-1.586951072414537</v>
-      </c>
-      <c r="D101">
-        <v>2.106948927585463</v>
-      </c>
-      <c r="E101">
-        <v>8.523899999999999</v>
-      </c>
-      <c r="F101">
-        <v>8.523899999999999</v>
-      </c>
-      <c r="G101">
-        <v>4.83</v>
-      </c>
-      <c r="H101">
-        <v>8.609999999999999</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.19</v>
-      </c>
-      <c r="K101">
-        <v>0.462</v>
-      </c>
-      <c r="L101">
-        <v>0.728</v>
-      </c>
-      <c r="M101">
-        <v>2.00993562</v>
-      </c>
-      <c r="N101">
-        <v>-1.28193562</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-1.28193562</v>
-      </c>
-      <c r="Q101">
-        <v>-0.8199356199999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.251886508720236</v>
-      </c>
-      <c r="T101">
-        <v>95.35130270927485</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2358</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3622006559593187</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
